--- a/Sindicatos Mediador.xlsx
+++ b/Sindicatos Mediador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Remuneração e Benefícios\SINDICAIS\Mediador\Base de Dados Excel Robô\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\165973\Desktop\Mediador\mediador exe V3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7DA144-94EC-42F7-8605-892029F1D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E3B4B9-D000-4114-B124-F21920D6EB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17789,7 +17789,7 @@
       </c>
       <c r="X2" s="11">
         <f ca="1">W2-TODAY()</f>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="X3" s="11">
         <f t="shared" ref="X3:X66" ca="1" si="0">W3-TODAY()</f>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="X4" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="X5" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="X6" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="X7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="X8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="X9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="X10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="X11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="X12" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="X13" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -18466,7 +18466,7 @@
       </c>
       <c r="X14" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="X15" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="X16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="X17" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="X18" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-398</v>
+        <v>-520</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="X19" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="X20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="X21" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="X22" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="X23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="X24" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="X25" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="X26" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="X27" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="X28" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="X29" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="X30" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-764</v>
+        <v>-886</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="X31" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="X32" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-398</v>
+        <v>-520</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="X33" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="X34" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="X35" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-825</v>
+        <v>-947</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="X36" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="X37" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="X38" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="X39" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="X40" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="X41" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="X42" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="X43" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="X44" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="X45" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="X46" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-428</v>
+        <v>-550</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="X47" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="X48" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="X49" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="X50" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="X51" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="X52" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="X53" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="X54" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="X55" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="X56" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="X57" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="X58" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="X59" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
@@ -20865,7 +20865,7 @@
       </c>
       <c r="X60" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="X61" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="X62" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="X63" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="X64" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.3">
@@ -21134,7 +21134,7 @@
       </c>
       <c r="X65" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.3">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="X66" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.3">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="X67" s="11">
         <f t="shared" ref="X67:X130" ca="1" si="1">W67-TODAY()</f>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.3">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="X68" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.3">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="X69" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.3">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="X70" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.3">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="X71" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.3">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="X72" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.3">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="X73" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-488</v>
+        <v>-610</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.3">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="X74" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.3">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="X75" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.3">
@@ -21704,7 +21704,7 @@
       </c>
       <c r="X76" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.3">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="X77" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.3">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="X78" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.3">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="X79" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>424</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="X80" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.3">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="X81" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.3">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="X82" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.3">
@@ -22065,7 +22065,7 @@
       </c>
       <c r="X83" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="X84" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.3">
@@ -22169,7 +22169,7 @@
       </c>
       <c r="X85" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.3">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="X86" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.3">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="X87" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.3">
@@ -22328,7 +22328,7 @@
       </c>
       <c r="X88" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.3">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="X89" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.3">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="X90" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.3">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="X91" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.3">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="X92" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.3">
@@ -22588,7 +22588,7 @@
       </c>
       <c r="X93" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.3">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="X94" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.3">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="X95" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.3">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="X96" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.3">
@@ -22796,7 +22796,7 @@
       </c>
       <c r="X97" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.3">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="X98" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.3">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="X99" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="X100" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.3">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="X101" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.3">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="X102" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="X103" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.3">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="X104" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.3">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="X105" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
@@ -23261,7 +23261,7 @@
       </c>
       <c r="X106" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.3">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="X107" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.3">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="X108" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.3">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="X109" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.3">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="X110" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="X111" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.3">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="X112" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="X113" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
@@ -23671,7 +23671,7 @@
       </c>
       <c r="X114" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.3">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="X115" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="X116" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.3">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="X117" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="X118" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.3">
@@ -23922,7 +23922,7 @@
       </c>
       <c r="X119" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.3">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="X120" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.3">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="X121" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.3">
@@ -24075,7 +24075,7 @@
       </c>
       <c r="X122" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.3">
@@ -24122,7 +24122,7 @@
       </c>
       <c r="X123" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.3">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="X124" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.3">
@@ -24223,7 +24223,7 @@
       </c>
       <c r="X125" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.3">
@@ -24275,7 +24275,7 @@
       </c>
       <c r="X126" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.3">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="X127" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.3">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="X128" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-3016</v>
+        <v>-3138</v>
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.3">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="X129" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-4112</v>
+        <v>-4234</v>
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.3">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="X130" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.3">
@@ -24527,7 +24527,7 @@
       </c>
       <c r="X131" s="11">
         <f t="shared" ref="X131:X194" ca="1" si="2">W131-TODAY()</f>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.3">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="X132" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.3">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="X133" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.3">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="X134" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.3">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="X135" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.3">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="X136" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.3">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="X137" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.3">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="X138" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.3">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="X139" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.3">
@@ -24995,7 +24995,7 @@
       </c>
       <c r="X140" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.3">
@@ -25047,7 +25047,7 @@
       </c>
       <c r="X141" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.3">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="X142" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.3">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="X143" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.3">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="X144" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.3">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="X145" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.3">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="X146" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.3">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="X147" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.3">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="X148" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.3">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="X149" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.3">
@@ -25524,7 +25524,7 @@
       </c>
       <c r="X150" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.3">
@@ -25576,7 +25576,7 @@
       </c>
       <c r="X151" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.3">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="X152" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.3">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="X153" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.3">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="X154" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.3">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="X155" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.3">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="X156" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.3">
@@ -25885,7 +25885,7 @@
       </c>
       <c r="X157" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.3">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="X158" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.3">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="X159" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.3">
@@ -26038,7 +26038,7 @@
       </c>
       <c r="X160" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.3">
@@ -26090,7 +26090,7 @@
       </c>
       <c r="X161" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.3">
@@ -26142,7 +26142,7 @@
       </c>
       <c r="X162" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.3">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="X163" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>424</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.3">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="X164" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-306</v>
+        <v>-428</v>
       </c>
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.3">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="X165" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="166" spans="1:24" x14ac:dyDescent="0.3">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="X166" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:24" x14ac:dyDescent="0.3">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="X167" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="168" spans="1:24" x14ac:dyDescent="0.3">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="X168" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>424</v>
+        <v>302</v>
       </c>
     </row>
     <row r="169" spans="1:24" x14ac:dyDescent="0.3">
@@ -26495,7 +26495,7 @@
       </c>
       <c r="X169" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="170" spans="1:24" x14ac:dyDescent="0.3">
@@ -26547,7 +26547,7 @@
       </c>
       <c r="X170" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="171" spans="1:24" x14ac:dyDescent="0.3">
@@ -26599,7 +26599,7 @@
       </c>
       <c r="X171" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:24" x14ac:dyDescent="0.3">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="X172" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="173" spans="1:24" x14ac:dyDescent="0.3">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="X173" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="174" spans="1:24" x14ac:dyDescent="0.3">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="X174" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="175" spans="1:24" x14ac:dyDescent="0.3">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="X175" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="176" spans="1:24" x14ac:dyDescent="0.3">
@@ -26859,7 +26859,7 @@
       </c>
       <c r="X176" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.3">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="X177" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.3">
@@ -26963,7 +26963,7 @@
       </c>
       <c r="X178" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="179" spans="1:24" x14ac:dyDescent="0.3">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="X179" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="180" spans="1:24" x14ac:dyDescent="0.3">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="X180" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="181" spans="1:24" x14ac:dyDescent="0.3">
@@ -27113,7 +27113,7 @@
       </c>
       <c r="X181" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="182" spans="1:24" x14ac:dyDescent="0.3">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="X182" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="183" spans="1:24" x14ac:dyDescent="0.3">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="X183" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-488</v>
+        <v>-610</v>
       </c>
     </row>
     <row r="184" spans="1:24" x14ac:dyDescent="0.3">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="X184" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="185" spans="1:24" x14ac:dyDescent="0.3">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="X185" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="186" spans="1:24" x14ac:dyDescent="0.3">
@@ -27371,7 +27371,7 @@
       </c>
       <c r="X186" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="187" spans="1:24" x14ac:dyDescent="0.3">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="X187" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-488</v>
+        <v>-610</v>
       </c>
     </row>
     <row r="188" spans="1:24" x14ac:dyDescent="0.3">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="X188" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="189" spans="1:24" x14ac:dyDescent="0.3">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="X189" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="190" spans="1:24" x14ac:dyDescent="0.3">
@@ -27565,7 +27565,7 @@
       </c>
       <c r="X190" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="191" spans="1:24" x14ac:dyDescent="0.3">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="X191" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="192" spans="1:24" x14ac:dyDescent="0.3">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="X192" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="193" spans="1:24" x14ac:dyDescent="0.3">
@@ -27721,7 +27721,7 @@
       </c>
       <c r="X193" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="194" spans="1:24" x14ac:dyDescent="0.3">
@@ -27773,7 +27773,7 @@
       </c>
       <c r="X194" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="195" spans="1:24" x14ac:dyDescent="0.3">
@@ -27822,7 +27822,7 @@
       </c>
       <c r="X195" s="11">
         <f t="shared" ref="X195:X258" ca="1" si="3">W195-TODAY()</f>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.3">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="X196" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="197" spans="1:24" x14ac:dyDescent="0.3">
@@ -27923,7 +27923,7 @@
       </c>
       <c r="X197" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="198" spans="1:24" x14ac:dyDescent="0.3">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="X198" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="199" spans="1:24" x14ac:dyDescent="0.3">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="X199" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="200" spans="1:24" x14ac:dyDescent="0.3">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="X200" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>212</v>
+        <v>90</v>
       </c>
     </row>
     <row r="201" spans="1:24" x14ac:dyDescent="0.3">
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X201" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="202" spans="1:24" x14ac:dyDescent="0.3">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="X202" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>212</v>
+        <v>90</v>
       </c>
     </row>
     <row r="203" spans="1:24" x14ac:dyDescent="0.3">
@@ -28217,7 +28217,7 @@
       </c>
       <c r="X203" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="204" spans="1:24" x14ac:dyDescent="0.3">
@@ -28266,7 +28266,7 @@
       </c>
       <c r="X204" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="205" spans="1:24" x14ac:dyDescent="0.3">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="X205" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="206" spans="1:24" x14ac:dyDescent="0.3">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="X206" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-398</v>
+        <v>-520</v>
       </c>
     </row>
     <row r="207" spans="1:24" x14ac:dyDescent="0.3">
@@ -28413,7 +28413,7 @@
       </c>
       <c r="X207" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>210</v>
       </c>
     </row>
     <row r="208" spans="1:24" x14ac:dyDescent="0.3">
@@ -28462,7 +28462,7 @@
       </c>
       <c r="X208" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="209" spans="1:24" x14ac:dyDescent="0.3">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="X209" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="210" spans="1:24" x14ac:dyDescent="0.3">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="X210" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="211" spans="1:24" x14ac:dyDescent="0.3">
@@ -28618,7 +28618,7 @@
       </c>
       <c r="X211" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.3">
@@ -28667,7 +28667,7 @@
       </c>
       <c r="X212" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="213" spans="1:24" x14ac:dyDescent="0.3">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="X213" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>210</v>
       </c>
     </row>
     <row r="214" spans="1:24" x14ac:dyDescent="0.3">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="X214" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215" spans="1:24" x14ac:dyDescent="0.3">
@@ -28814,7 +28814,7 @@
       </c>
       <c r="X215" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="216" spans="1:24" x14ac:dyDescent="0.3">
@@ -28866,7 +28866,7 @@
       </c>
       <c r="X216" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="217" spans="1:24" x14ac:dyDescent="0.3">
@@ -28915,7 +28915,7 @@
       </c>
       <c r="X217" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="218" spans="1:24" x14ac:dyDescent="0.3">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="X218" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="219" spans="1:24" x14ac:dyDescent="0.3">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="X219" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="220" spans="1:24" x14ac:dyDescent="0.3">
@@ -29068,7 +29068,7 @@
       </c>
       <c r="X220" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="221" spans="1:24" x14ac:dyDescent="0.3">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="X221" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="222" spans="1:24" x14ac:dyDescent="0.3">
@@ -29172,7 +29172,7 @@
       </c>
       <c r="X222" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-428</v>
+        <v>-550</v>
       </c>
     </row>
     <row r="223" spans="1:24" x14ac:dyDescent="0.3">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="X223" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="224" spans="1:24" x14ac:dyDescent="0.3">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="X224" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="225" spans="1:24" x14ac:dyDescent="0.3">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="X225" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="226" spans="1:24" x14ac:dyDescent="0.3">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="X226" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-306</v>
+        <v>-428</v>
       </c>
     </row>
     <row r="227" spans="1:24" x14ac:dyDescent="0.3">
@@ -29427,7 +29427,7 @@
       </c>
       <c r="X227" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="228" spans="1:24" x14ac:dyDescent="0.3">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="X228" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="229" spans="1:24" x14ac:dyDescent="0.3">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="X229" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>210</v>
       </c>
     </row>
     <row r="230" spans="1:24" x14ac:dyDescent="0.3">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="X230" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="231" spans="1:24" x14ac:dyDescent="0.3">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="X231" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="232" spans="1:24" x14ac:dyDescent="0.3">
@@ -29676,7 +29676,7 @@
       </c>
       <c r="X232" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="233" spans="1:24" x14ac:dyDescent="0.3">
@@ -29728,7 +29728,7 @@
       </c>
       <c r="X233" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="234" spans="1:24" x14ac:dyDescent="0.3">
@@ -29777,7 +29777,7 @@
       </c>
       <c r="X234" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="235" spans="1:24" x14ac:dyDescent="0.3">
@@ -29826,7 +29826,7 @@
       </c>
       <c r="X235" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="236" spans="1:24" x14ac:dyDescent="0.3">
@@ -29875,7 +29875,7 @@
       </c>
       <c r="X236" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="237" spans="1:24" x14ac:dyDescent="0.3">
@@ -29924,7 +29924,7 @@
       </c>
       <c r="X237" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="238" spans="1:24" x14ac:dyDescent="0.3">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="X238" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="239" spans="1:24" x14ac:dyDescent="0.3">
@@ -30028,7 +30028,7 @@
       </c>
       <c r="X239" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="240" spans="1:24" x14ac:dyDescent="0.3">
@@ -30080,7 +30080,7 @@
       </c>
       <c r="X240" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="241" spans="1:24" x14ac:dyDescent="0.3">
@@ -30129,7 +30129,7 @@
       </c>
       <c r="X241" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="242" spans="1:24" x14ac:dyDescent="0.3">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="X242" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="243" spans="1:24" x14ac:dyDescent="0.3">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="X243" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="244" spans="1:24" x14ac:dyDescent="0.3">
@@ -30282,7 +30282,7 @@
       </c>
       <c r="X244" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="245" spans="1:24" x14ac:dyDescent="0.3">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="X245" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="246" spans="1:24" x14ac:dyDescent="0.3">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="X246" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="247" spans="1:24" x14ac:dyDescent="0.3">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="X247" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="248" spans="1:24" x14ac:dyDescent="0.3">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="X248" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="249" spans="1:24" x14ac:dyDescent="0.3">
@@ -30548,7 +30548,7 @@
       </c>
       <c r="X249" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="250" spans="1:24" x14ac:dyDescent="0.3">
@@ -30597,7 +30597,7 @@
       </c>
       <c r="X250" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>210</v>
       </c>
     </row>
     <row r="251" spans="1:24" x14ac:dyDescent="0.3">
@@ -30649,7 +30649,7 @@
       </c>
       <c r="X251" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="252" spans="1:24" x14ac:dyDescent="0.3">
@@ -30701,7 +30701,7 @@
       </c>
       <c r="X252" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="253" spans="1:24" x14ac:dyDescent="0.3">
@@ -30753,7 +30753,7 @@
       </c>
       <c r="X253" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="254" spans="1:24" x14ac:dyDescent="0.3">
@@ -30802,7 +30802,7 @@
       </c>
       <c r="X254" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="255" spans="1:24" x14ac:dyDescent="0.3">
@@ -30851,7 +30851,7 @@
       </c>
       <c r="X255" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="256" spans="1:24" x14ac:dyDescent="0.3">
@@ -30903,7 +30903,7 @@
       </c>
       <c r="X256" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="257" spans="1:24" x14ac:dyDescent="0.3">
@@ -30955,7 +30955,7 @@
       </c>
       <c r="X257" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="258" spans="1:24" x14ac:dyDescent="0.3">
@@ -31007,7 +31007,7 @@
       </c>
       <c r="X258" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="259" spans="1:24" x14ac:dyDescent="0.3">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="X259" s="11">
         <f t="shared" ref="X259:X322" ca="1" si="4">W259-TODAY()</f>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="260" spans="1:24" x14ac:dyDescent="0.3">
@@ -31105,7 +31105,7 @@
       </c>
       <c r="X260" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>424</v>
+        <v>302</v>
       </c>
     </row>
     <row r="261" spans="1:24" x14ac:dyDescent="0.3">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="X261" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="262" spans="1:24" x14ac:dyDescent="0.3">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="X262" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="263" spans="1:24" x14ac:dyDescent="0.3">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="X263" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="264" spans="1:24" x14ac:dyDescent="0.3">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="X264" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="265" spans="1:24" x14ac:dyDescent="0.3">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="X265" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="266" spans="1:24" x14ac:dyDescent="0.3">
@@ -31417,7 +31417,7 @@
       </c>
       <c r="X266" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-825</v>
+        <v>-947</v>
       </c>
     </row>
     <row r="267" spans="1:24" x14ac:dyDescent="0.3">
@@ -31469,7 +31469,7 @@
       </c>
       <c r="X267" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="268" spans="1:24" x14ac:dyDescent="0.3">
@@ -31521,7 +31521,7 @@
       </c>
       <c r="X268" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="269" spans="1:24" x14ac:dyDescent="0.3">
@@ -31573,7 +31573,7 @@
       </c>
       <c r="X269" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="270" spans="1:24" x14ac:dyDescent="0.3">
@@ -31625,7 +31625,7 @@
       </c>
       <c r="X270" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="271" spans="1:24" x14ac:dyDescent="0.3">
@@ -31677,7 +31677,7 @@
       </c>
       <c r="X271" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="272" spans="1:24" x14ac:dyDescent="0.3">
@@ -31738,7 +31738,7 @@
       </c>
       <c r="X272" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="273" spans="1:24" x14ac:dyDescent="0.3">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="X273" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-3016</v>
+        <v>-3138</v>
       </c>
     </row>
     <row r="274" spans="1:24" x14ac:dyDescent="0.3">
@@ -31837,7 +31837,7 @@
       </c>
       <c r="X274" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="275" spans="1:24" x14ac:dyDescent="0.3">
@@ -31895,7 +31895,7 @@
       </c>
       <c r="X275" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="276" spans="1:24" x14ac:dyDescent="0.3">
@@ -31947,7 +31947,7 @@
       </c>
       <c r="X276" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="277" spans="1:24" x14ac:dyDescent="0.3">
@@ -31999,7 +31999,7 @@
       </c>
       <c r="X277" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="278" spans="1:24" x14ac:dyDescent="0.3">
@@ -32048,7 +32048,7 @@
       </c>
       <c r="X278" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="279" spans="1:24" x14ac:dyDescent="0.3">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="X279" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="280" spans="1:24" x14ac:dyDescent="0.3">
@@ -32152,7 +32152,7 @@
       </c>
       <c r="X280" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="281" spans="1:24" x14ac:dyDescent="0.3">
@@ -32204,7 +32204,7 @@
       </c>
       <c r="X281" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="282" spans="1:24" x14ac:dyDescent="0.3">
@@ -32256,7 +32256,7 @@
       </c>
       <c r="X282" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="283" spans="1:24" x14ac:dyDescent="0.3">
@@ -32305,7 +32305,7 @@
       </c>
       <c r="X283" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="284" spans="1:24" x14ac:dyDescent="0.3">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="X284" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="285" spans="1:24" x14ac:dyDescent="0.3">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="X285" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="286" spans="1:24" x14ac:dyDescent="0.3">
@@ -32458,7 +32458,7 @@
       </c>
       <c r="X286" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="287" spans="1:24" x14ac:dyDescent="0.3">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="X287" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="288" spans="1:24" x14ac:dyDescent="0.3">
@@ -32556,7 +32556,7 @@
       </c>
       <c r="X288" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="289" spans="1:24" x14ac:dyDescent="0.3">
@@ -32605,7 +32605,7 @@
       </c>
       <c r="X289" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="290" spans="1:24" x14ac:dyDescent="0.3">
@@ -32654,7 +32654,7 @@
       </c>
       <c r="X290" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="291" spans="1:24" x14ac:dyDescent="0.3">
@@ -32706,7 +32706,7 @@
       </c>
       <c r="X291" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="292" spans="1:24" x14ac:dyDescent="0.3">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="X292" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="293" spans="1:24" x14ac:dyDescent="0.3">
@@ -32810,7 +32810,7 @@
       </c>
       <c r="X293" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="294" spans="1:24" x14ac:dyDescent="0.3">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="X294" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="295" spans="1:24" x14ac:dyDescent="0.3">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="X295" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="296" spans="1:24" x14ac:dyDescent="0.3">
@@ -32963,7 +32963,7 @@
       </c>
       <c r="X296" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="297" spans="1:24" x14ac:dyDescent="0.3">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="X297" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="298" spans="1:24" x14ac:dyDescent="0.3">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="X298" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="299" spans="1:24" x14ac:dyDescent="0.3">
@@ -33113,7 +33113,7 @@
       </c>
       <c r="X299" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="300" spans="1:24" x14ac:dyDescent="0.3">
@@ -33165,7 +33165,7 @@
       </c>
       <c r="X300" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="301" spans="1:24" x14ac:dyDescent="0.3">
@@ -33212,7 +33212,7 @@
       </c>
       <c r="X301" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-488</v>
+        <v>-610</v>
       </c>
     </row>
     <row r="302" spans="1:24" x14ac:dyDescent="0.3">
@@ -33261,7 +33261,7 @@
       </c>
       <c r="X302" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="303" spans="1:24" x14ac:dyDescent="0.3">
@@ -33313,7 +33313,7 @@
       </c>
       <c r="X303" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="304" spans="1:24" x14ac:dyDescent="0.3">
@@ -33365,7 +33365,7 @@
       </c>
       <c r="X304" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="305" spans="1:24" x14ac:dyDescent="0.3">
@@ -33414,7 +33414,7 @@
       </c>
       <c r="X305" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="306" spans="1:24" x14ac:dyDescent="0.3">
@@ -33469,7 +33469,7 @@
       </c>
       <c r="X306" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="307" spans="1:24" x14ac:dyDescent="0.3">
@@ -33521,7 +33521,7 @@
       </c>
       <c r="X307" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="308" spans="1:24" x14ac:dyDescent="0.3">
@@ -33570,7 +33570,7 @@
       </c>
       <c r="X308" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="309" spans="1:24" x14ac:dyDescent="0.3">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="X309" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="310" spans="1:24" x14ac:dyDescent="0.3">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="X310" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="311" spans="1:24" x14ac:dyDescent="0.3">
@@ -33726,7 +33726,7 @@
       </c>
       <c r="X311" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="312" spans="1:24" x14ac:dyDescent="0.3">
@@ -33775,7 +33775,7 @@
       </c>
       <c r="X312" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="313" spans="1:24" x14ac:dyDescent="0.3">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="X313" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="314" spans="1:24" x14ac:dyDescent="0.3">
@@ -33873,7 +33873,7 @@
       </c>
       <c r="X314" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="315" spans="1:24" x14ac:dyDescent="0.3">
@@ -33922,7 +33922,7 @@
       </c>
       <c r="X315" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="316" spans="1:24" x14ac:dyDescent="0.3">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="X316" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="317" spans="1:24" x14ac:dyDescent="0.3">
@@ -34020,7 +34020,7 @@
       </c>
       <c r="X317" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="318" spans="1:24" x14ac:dyDescent="0.3">
@@ -34067,7 +34067,7 @@
       </c>
       <c r="X318" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="319" spans="1:24" x14ac:dyDescent="0.3">
@@ -34116,7 +34116,7 @@
       </c>
       <c r="X319" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>332</v>
+        <v>210</v>
       </c>
     </row>
     <row r="320" spans="1:24" x14ac:dyDescent="0.3">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="X320" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="321" spans="1:24" x14ac:dyDescent="0.3">
@@ -34215,7 +34215,7 @@
       </c>
       <c r="X321" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-488</v>
+        <v>-610</v>
       </c>
     </row>
     <row r="322" spans="1:24" x14ac:dyDescent="0.3">
@@ -34264,7 +34264,7 @@
       </c>
       <c r="X322" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="323" spans="1:24" x14ac:dyDescent="0.3">
@@ -34313,7 +34313,7 @@
       </c>
       <c r="X323" s="11">
         <f t="shared" ref="X323:X386" ca="1" si="5">W323-TODAY()</f>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="324" spans="1:24" x14ac:dyDescent="0.3">
@@ -34362,7 +34362,7 @@
       </c>
       <c r="X324" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="325" spans="1:24" x14ac:dyDescent="0.3">
@@ -34411,7 +34411,7 @@
       </c>
       <c r="X325" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="326" spans="1:24" x14ac:dyDescent="0.3">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="X326" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="327" spans="1:24" x14ac:dyDescent="0.3">
@@ -34512,7 +34512,7 @@
       </c>
       <c r="X327" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="328" spans="1:24" x14ac:dyDescent="0.3">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="X328" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="329" spans="1:24" x14ac:dyDescent="0.3">
@@ -34610,7 +34610,7 @@
       </c>
       <c r="X329" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="330" spans="1:24" x14ac:dyDescent="0.3">
@@ -34659,7 +34659,7 @@
       </c>
       <c r="X330" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="331" spans="1:24" x14ac:dyDescent="0.3">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="X331" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="332" spans="1:24" x14ac:dyDescent="0.3">
@@ -34757,7 +34757,7 @@
       </c>
       <c r="X332" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="333" spans="1:24" x14ac:dyDescent="0.3">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="X333" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="334" spans="1:24" x14ac:dyDescent="0.3">
@@ -34870,7 +34870,7 @@
       </c>
       <c r="X334" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="335" spans="1:24" x14ac:dyDescent="0.3">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="X335" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-3016</v>
+        <v>-3138</v>
       </c>
     </row>
     <row r="336" spans="1:24" x14ac:dyDescent="0.3">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="X336" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="337" spans="1:24" x14ac:dyDescent="0.3">
@@ -35015,7 +35015,7 @@
       </c>
       <c r="X337" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="338" spans="1:24" x14ac:dyDescent="0.3">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="X338" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="339" spans="1:24" x14ac:dyDescent="0.3">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="X339" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="340" spans="1:24" x14ac:dyDescent="0.3">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="X340" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="341" spans="1:24" x14ac:dyDescent="0.3">
@@ -35214,7 +35214,7 @@
       </c>
       <c r="X341" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="342" spans="1:24" x14ac:dyDescent="0.3">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="X342" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="343" spans="1:24" x14ac:dyDescent="0.3">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="X343" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="344" spans="1:24" x14ac:dyDescent="0.3">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="X344" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="345" spans="1:24" x14ac:dyDescent="0.3">
@@ -35416,7 +35416,7 @@
       </c>
       <c r="X345" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-122</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="346" spans="1:24" x14ac:dyDescent="0.3">
@@ -35462,7 +35462,7 @@
       </c>
       <c r="X346" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="347" spans="1:24" x14ac:dyDescent="0.3">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="X347" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="348" spans="1:24" x14ac:dyDescent="0.3">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="X348" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="349" spans="1:24" x14ac:dyDescent="0.3">
@@ -35615,7 +35615,7 @@
       </c>
       <c r="X349" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="350" spans="1:24" x14ac:dyDescent="0.3">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="X350" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="351" spans="1:24" x14ac:dyDescent="0.3">
@@ -35713,7 +35713,7 @@
       </c>
       <c r="X351" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="352" spans="1:24" x14ac:dyDescent="0.3">
@@ -35762,7 +35762,7 @@
       </c>
       <c r="X352" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="353" spans="1:24" x14ac:dyDescent="0.3">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="X353" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="354" spans="1:24" x14ac:dyDescent="0.3">
@@ -35860,7 +35860,7 @@
       </c>
       <c r="X354" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="355" spans="1:24" x14ac:dyDescent="0.3">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="X355" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-672</v>
+        <v>-794</v>
       </c>
     </row>
     <row r="356" spans="1:24" x14ac:dyDescent="0.3">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="X356" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="357" spans="1:24" x14ac:dyDescent="0.3">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="X357" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="358" spans="1:24" x14ac:dyDescent="0.3">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="X358" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="359" spans="1:24" x14ac:dyDescent="0.3">
@@ -36111,7 +36111,7 @@
       </c>
       <c r="X359" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="360" spans="1:24" x14ac:dyDescent="0.3">
@@ -36160,7 +36160,7 @@
       </c>
       <c r="X360" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="361" spans="1:24" x14ac:dyDescent="0.3">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="X361" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="362" spans="1:24" x14ac:dyDescent="0.3">
@@ -36261,7 +36261,7 @@
       </c>
       <c r="X362" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="363" spans="1:24" x14ac:dyDescent="0.3">
@@ -36310,7 +36310,7 @@
       </c>
       <c r="X363" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="364" spans="1:24" x14ac:dyDescent="0.3">
@@ -36362,7 +36362,7 @@
       </c>
       <c r="X364" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="365" spans="1:24" x14ac:dyDescent="0.3">
@@ -36414,7 +36414,7 @@
       </c>
       <c r="X365" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="366" spans="1:24" x14ac:dyDescent="0.3">
@@ -36463,7 +36463,7 @@
       </c>
       <c r="X366" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="367" spans="1:24" x14ac:dyDescent="0.3">
@@ -36512,7 +36512,7 @@
       </c>
       <c r="X367" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="368" spans="1:24" x14ac:dyDescent="0.3">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="X368" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="369" spans="1:24" x14ac:dyDescent="0.3">
@@ -36619,7 +36619,7 @@
       </c>
       <c r="X369" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="370" spans="1:24" x14ac:dyDescent="0.3">
@@ -36671,7 +36671,7 @@
       </c>
       <c r="X370" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="371" spans="1:24" x14ac:dyDescent="0.3">
@@ -36720,7 +36720,7 @@
       </c>
       <c r="X371" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="372" spans="1:24" x14ac:dyDescent="0.3">
@@ -36776,7 +36776,7 @@
       </c>
       <c r="X372" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-4112</v>
+        <v>-4234</v>
       </c>
     </row>
     <row r="373" spans="1:24" x14ac:dyDescent="0.3">
@@ -36828,7 +36828,7 @@
       </c>
       <c r="X373" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="374" spans="1:24" x14ac:dyDescent="0.3">
@@ -36880,7 +36880,7 @@
       </c>
       <c r="X374" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="375" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="X375" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="376" spans="1:24" x14ac:dyDescent="0.3">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="X376" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="377" spans="1:24" x14ac:dyDescent="0.3">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="X377" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>363</v>
+        <v>241</v>
       </c>
     </row>
     <row r="378" spans="1:24" x14ac:dyDescent="0.3">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="X378" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="379" spans="1:24" x14ac:dyDescent="0.3">
@@ -37137,7 +37137,7 @@
       </c>
       <c r="X379" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="380" spans="1:24" x14ac:dyDescent="0.3">
@@ -37186,7 +37186,7 @@
       </c>
       <c r="X380" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="381" spans="1:24" x14ac:dyDescent="0.3">
@@ -37235,7 +37235,7 @@
       </c>
       <c r="X381" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="382" spans="1:24" x14ac:dyDescent="0.3">
@@ -37284,7 +37284,7 @@
       </c>
       <c r="X382" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="383" spans="1:24" x14ac:dyDescent="0.3">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="X383" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="384" spans="1:24" x14ac:dyDescent="0.3">
@@ -37385,7 +37385,7 @@
       </c>
       <c r="X384" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-306</v>
+        <v>-428</v>
       </c>
     </row>
     <row r="385" spans="1:24" x14ac:dyDescent="0.3">
@@ -37434,7 +37434,7 @@
       </c>
       <c r="X385" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="386" spans="1:24" x14ac:dyDescent="0.3">
@@ -37483,7 +37483,7 @@
       </c>
       <c r="X386" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="387" spans="1:24" x14ac:dyDescent="0.3">
@@ -37532,7 +37532,7 @@
       </c>
       <c r="X387" s="11">
         <f t="shared" ref="X387:X450" ca="1" si="6">W387-TODAY()</f>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="388" spans="1:24" x14ac:dyDescent="0.3">
@@ -37581,7 +37581,7 @@
       </c>
       <c r="X388" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="389" spans="1:24" x14ac:dyDescent="0.3">
@@ -37627,7 +37627,7 @@
       </c>
       <c r="X389" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="390" spans="1:24" x14ac:dyDescent="0.3">
@@ -37673,7 +37673,7 @@
       </c>
       <c r="X390" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="391" spans="1:24" x14ac:dyDescent="0.3">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="X391" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="392" spans="1:24" x14ac:dyDescent="0.3">
@@ -37774,7 +37774,7 @@
       </c>
       <c r="X392" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="393" spans="1:24" x14ac:dyDescent="0.3">
@@ -37823,7 +37823,7 @@
       </c>
       <c r="X393" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="394" spans="1:24" x14ac:dyDescent="0.3">
@@ -37884,7 +37884,7 @@
       </c>
       <c r="X394" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="395" spans="1:24" x14ac:dyDescent="0.3">
@@ -37936,7 +37936,7 @@
       </c>
       <c r="X395" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="396" spans="1:24" x14ac:dyDescent="0.3">
@@ -37988,7 +37988,7 @@
       </c>
       <c r="X396" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="397" spans="1:24" x14ac:dyDescent="0.3">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="X397" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="398" spans="1:24" x14ac:dyDescent="0.3">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="X398" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="399" spans="1:24" x14ac:dyDescent="0.3">
@@ -38132,7 +38132,7 @@
       </c>
       <c r="X399" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="400" spans="1:24" x14ac:dyDescent="0.3">
@@ -38181,7 +38181,7 @@
       </c>
       <c r="X400" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="401" spans="1:24" x14ac:dyDescent="0.3">
@@ -38230,7 +38230,7 @@
       </c>
       <c r="X401" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="402" spans="1:24" x14ac:dyDescent="0.3">
@@ -38282,7 +38282,7 @@
       </c>
       <c r="X402" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="403" spans="1:24" x14ac:dyDescent="0.3">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="X403" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="404" spans="1:24" x14ac:dyDescent="0.3">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="X404" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="405" spans="1:24" x14ac:dyDescent="0.3">
@@ -38435,7 +38435,7 @@
       </c>
       <c r="X405" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="406" spans="1:24" x14ac:dyDescent="0.3">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="X406" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="407" spans="1:24" x14ac:dyDescent="0.3">
@@ -38539,7 +38539,7 @@
       </c>
       <c r="X407" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="408" spans="1:24" x14ac:dyDescent="0.3">
@@ -38588,7 +38588,7 @@
       </c>
       <c r="X408" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="409" spans="1:24" x14ac:dyDescent="0.3">
@@ -38640,7 +38640,7 @@
       </c>
       <c r="X409" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="410" spans="1:24" x14ac:dyDescent="0.3">
@@ -38692,7 +38692,7 @@
       </c>
       <c r="X410" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="411" spans="1:24" x14ac:dyDescent="0.3">
@@ -38741,7 +38741,7 @@
       </c>
       <c r="X411" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="412" spans="1:24" x14ac:dyDescent="0.3">
@@ -38787,7 +38787,7 @@
       </c>
       <c r="X412" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="413" spans="1:24" x14ac:dyDescent="0.3">
@@ -38836,7 +38836,7 @@
       </c>
       <c r="X413" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="414" spans="1:24" x14ac:dyDescent="0.3">
@@ -38888,7 +38888,7 @@
       </c>
       <c r="X414" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
     <row r="415" spans="1:24" x14ac:dyDescent="0.3">
@@ -38937,7 +38937,7 @@
       </c>
       <c r="X415" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="416" spans="1:24" x14ac:dyDescent="0.3">
@@ -38986,7 +38986,7 @@
       </c>
       <c r="X416" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="417" spans="1:24" x14ac:dyDescent="0.3">
@@ -39035,7 +39035,7 @@
       </c>
       <c r="X417" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="418" spans="1:24" x14ac:dyDescent="0.3">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="X418" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="419" spans="1:24" x14ac:dyDescent="0.3">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="X419" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="420" spans="1:24" x14ac:dyDescent="0.3">
@@ -39182,7 +39182,7 @@
       </c>
       <c r="X420" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="421" spans="1:24" x14ac:dyDescent="0.3">
@@ -39231,7 +39231,7 @@
       </c>
       <c r="X421" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="422" spans="1:24" x14ac:dyDescent="0.3">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="X422" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="423" spans="1:24" x14ac:dyDescent="0.3">
@@ -39329,7 +39329,7 @@
       </c>
       <c r="X423" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="424" spans="1:24" x14ac:dyDescent="0.3">
@@ -39378,7 +39378,7 @@
       </c>
       <c r="X424" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="425" spans="1:24" x14ac:dyDescent="0.3">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="X425" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="426" spans="1:24" x14ac:dyDescent="0.3">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="X426" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="427" spans="1:24" x14ac:dyDescent="0.3">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="X427" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="428" spans="1:24" x14ac:dyDescent="0.3">
@@ -39574,7 +39574,7 @@
       </c>
       <c r="X428" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="429" spans="1:24" x14ac:dyDescent="0.3">
@@ -39623,7 +39623,7 @@
       </c>
       <c r="X429" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="430" spans="1:24" x14ac:dyDescent="0.3">
@@ -39672,7 +39672,7 @@
       </c>
       <c r="X430" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="431" spans="1:24" x14ac:dyDescent="0.3">
@@ -39721,7 +39721,7 @@
       </c>
       <c r="X431" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="432" spans="1:24" x14ac:dyDescent="0.3">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="X432" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="433" spans="1:24" x14ac:dyDescent="0.3">
@@ -39822,7 +39822,7 @@
       </c>
       <c r="X433" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="434" spans="1:24" x14ac:dyDescent="0.3">
@@ -39871,7 +39871,7 @@
       </c>
       <c r="X434" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="435" spans="1:24" x14ac:dyDescent="0.3">
@@ -39920,7 +39920,7 @@
       </c>
       <c r="X435" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="436" spans="1:24" x14ac:dyDescent="0.3">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="X436" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="437" spans="1:24" x14ac:dyDescent="0.3">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="X437" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="438" spans="1:24" x14ac:dyDescent="0.3">
@@ -40067,7 +40067,7 @@
       </c>
       <c r="X438" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="439" spans="1:24" x14ac:dyDescent="0.3">
@@ -40116,7 +40116,7 @@
       </c>
       <c r="X439" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="440" spans="1:24" x14ac:dyDescent="0.3">
@@ -40165,7 +40165,7 @@
       </c>
       <c r="X440" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="441" spans="1:24" x14ac:dyDescent="0.3">
@@ -40217,7 +40217,7 @@
       </c>
       <c r="X441" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="442" spans="1:24" x14ac:dyDescent="0.3">
@@ -40266,7 +40266,7 @@
       </c>
       <c r="X442" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="443" spans="1:24" x14ac:dyDescent="0.3">
@@ -40315,7 +40315,7 @@
       </c>
       <c r="X443" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="444" spans="1:24" x14ac:dyDescent="0.3">
@@ -40364,7 +40364,7 @@
       </c>
       <c r="X444" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="445" spans="1:24" x14ac:dyDescent="0.3">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="X445" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="446" spans="1:24" x14ac:dyDescent="0.3">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="X446" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="447" spans="1:24" x14ac:dyDescent="0.3">
@@ -40511,7 +40511,7 @@
       </c>
       <c r="X447" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="448" spans="1:24" x14ac:dyDescent="0.3">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="X448" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="449" spans="1:24" x14ac:dyDescent="0.3">
@@ -40609,7 +40609,7 @@
       </c>
       <c r="X449" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="450" spans="1:24" x14ac:dyDescent="0.3">
@@ -40658,7 +40658,7 @@
       </c>
       <c r="X450" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="451" spans="1:24" x14ac:dyDescent="0.3">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="X451" s="11">
         <f t="shared" ref="X451:X514" ca="1" si="7">W451-TODAY()</f>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="452" spans="1:24" x14ac:dyDescent="0.3">
@@ -40759,7 +40759,7 @@
       </c>
       <c r="X452" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="453" spans="1:24" x14ac:dyDescent="0.3">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="X453" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="454" spans="1:24" x14ac:dyDescent="0.3">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="X454" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="455" spans="1:24" x14ac:dyDescent="0.3">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="X455" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="456" spans="1:24" x14ac:dyDescent="0.3">
@@ -40958,7 +40958,7 @@
       </c>
       <c r="X456" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="457" spans="1:24" x14ac:dyDescent="0.3">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="X457" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="458" spans="1:24" x14ac:dyDescent="0.3">
@@ -41059,7 +41059,7 @@
       </c>
       <c r="X458" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="459" spans="1:24" x14ac:dyDescent="0.3">
@@ -41108,7 +41108,7 @@
       </c>
       <c r="X459" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="460" spans="1:24" x14ac:dyDescent="0.3">
@@ -41157,7 +41157,7 @@
       </c>
       <c r="X460" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="461" spans="1:24" x14ac:dyDescent="0.3">
@@ -41206,7 +41206,7 @@
       </c>
       <c r="X461" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="462" spans="1:24" x14ac:dyDescent="0.3">
@@ -41255,7 +41255,7 @@
       </c>
       <c r="X462" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="463" spans="1:24" x14ac:dyDescent="0.3">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="X463" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="464" spans="1:24" x14ac:dyDescent="0.3">
@@ -41350,7 +41350,7 @@
       </c>
       <c r="X464" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>363</v>
+        <v>241</v>
       </c>
     </row>
     <row r="465" spans="1:24" x14ac:dyDescent="0.3">
@@ -41399,7 +41399,7 @@
       </c>
       <c r="X465" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="466" spans="1:24" x14ac:dyDescent="0.3">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="X466" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="467" spans="1:24" x14ac:dyDescent="0.3">
@@ -41497,7 +41497,7 @@
       </c>
       <c r="X467" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="468" spans="1:24" x14ac:dyDescent="0.3">
@@ -41546,7 +41546,7 @@
       </c>
       <c r="X468" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="469" spans="1:24" x14ac:dyDescent="0.3">
@@ -41595,7 +41595,7 @@
       </c>
       <c r="X469" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="470" spans="1:24" x14ac:dyDescent="0.3">
@@ -41644,7 +41644,7 @@
       </c>
       <c r="X470" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="471" spans="1:24" x14ac:dyDescent="0.3">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="X471" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="472" spans="1:24" x14ac:dyDescent="0.3">
@@ -41742,7 +41742,7 @@
       </c>
       <c r="X472" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="473" spans="1:24" x14ac:dyDescent="0.3">
@@ -41791,7 +41791,7 @@
       </c>
       <c r="X473" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="474" spans="1:24" x14ac:dyDescent="0.3">
@@ -41840,7 +41840,7 @@
       </c>
       <c r="X474" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="475" spans="1:24" x14ac:dyDescent="0.3">
@@ -41892,7 +41892,7 @@
       </c>
       <c r="X475" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="476" spans="1:24" x14ac:dyDescent="0.3">
@@ -41944,7 +41944,7 @@
       </c>
       <c r="X476" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="477" spans="1:24" x14ac:dyDescent="0.3">
@@ -41993,7 +41993,7 @@
       </c>
       <c r="X477" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>363</v>
+        <v>241</v>
       </c>
     </row>
     <row r="478" spans="1:24" x14ac:dyDescent="0.3">
@@ -42042,7 +42042,7 @@
       </c>
       <c r="X478" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="479" spans="1:24" x14ac:dyDescent="0.3">
@@ -42091,7 +42091,7 @@
       </c>
       <c r="X479" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="480" spans="1:24" x14ac:dyDescent="0.3">
@@ -42140,7 +42140,7 @@
       </c>
       <c r="X480" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="481" spans="1:24" x14ac:dyDescent="0.3">
@@ -42192,7 +42192,7 @@
       </c>
       <c r="X481" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="482" spans="1:24" x14ac:dyDescent="0.3">
@@ -42241,7 +42241,7 @@
       </c>
       <c r="X482" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="483" spans="1:24" x14ac:dyDescent="0.3">
@@ -42290,7 +42290,7 @@
       </c>
       <c r="X483" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="484" spans="1:24" x14ac:dyDescent="0.3">
@@ -42339,7 +42339,7 @@
       </c>
       <c r="X484" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="485" spans="1:24" x14ac:dyDescent="0.3">
@@ -42388,7 +42388,7 @@
       </c>
       <c r="X485" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="486" spans="1:24" x14ac:dyDescent="0.3">
@@ -42437,7 +42437,7 @@
       </c>
       <c r="X486" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="487" spans="1:24" x14ac:dyDescent="0.3">
@@ -42489,7 +42489,7 @@
       </c>
       <c r="X487" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-63</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="488" spans="1:24" x14ac:dyDescent="0.3">
@@ -42538,7 +42538,7 @@
       </c>
       <c r="X488" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="489" spans="1:24" x14ac:dyDescent="0.3">
@@ -42590,7 +42590,7 @@
       </c>
       <c r="X489" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="490" spans="1:24" x14ac:dyDescent="0.3">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="X490" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="491" spans="1:24" x14ac:dyDescent="0.3">
@@ -42691,7 +42691,7 @@
       </c>
       <c r="X491" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="492" spans="1:24" x14ac:dyDescent="0.3">
@@ -42740,7 +42740,7 @@
       </c>
       <c r="X492" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="493" spans="1:24" x14ac:dyDescent="0.3">
@@ -42792,7 +42792,7 @@
       </c>
       <c r="X493" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>120</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="494" spans="1:24" x14ac:dyDescent="0.3">
@@ -42841,7 +42841,7 @@
       </c>
       <c r="X494" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="495" spans="1:24" x14ac:dyDescent="0.3">
@@ -42890,7 +42890,7 @@
       </c>
       <c r="X495" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="496" spans="1:24" x14ac:dyDescent="0.3">
@@ -42939,7 +42939,7 @@
       </c>
       <c r="X496" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="497" spans="1:24" x14ac:dyDescent="0.3">
@@ -42988,7 +42988,7 @@
       </c>
       <c r="X497" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="498" spans="1:24" x14ac:dyDescent="0.3">
@@ -43037,7 +43037,7 @@
       </c>
       <c r="X498" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="499" spans="1:24" x14ac:dyDescent="0.3">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="X499" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="500" spans="1:24" x14ac:dyDescent="0.3">
@@ -43138,7 +43138,7 @@
       </c>
       <c r="X500" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="501" spans="1:24" x14ac:dyDescent="0.3">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="X501" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="502" spans="1:24" x14ac:dyDescent="0.3">
@@ -43236,7 +43236,7 @@
       </c>
       <c r="X502" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="503" spans="1:24" x14ac:dyDescent="0.3">
@@ -43285,7 +43285,7 @@
       </c>
       <c r="X503" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="504" spans="1:24" x14ac:dyDescent="0.3">
@@ -43334,7 +43334,7 @@
       </c>
       <c r="X504" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="505" spans="1:24" x14ac:dyDescent="0.3">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="X505" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="506" spans="1:24" x14ac:dyDescent="0.3">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="X506" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="507" spans="1:24" x14ac:dyDescent="0.3">
@@ -43481,7 +43481,7 @@
       </c>
       <c r="X507" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="508" spans="1:24" x14ac:dyDescent="0.3">
@@ -43530,7 +43530,7 @@
       </c>
       <c r="X508" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="509" spans="1:24" x14ac:dyDescent="0.3">
@@ -43579,7 +43579,7 @@
       </c>
       <c r="X509" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="510" spans="1:24" x14ac:dyDescent="0.3">
@@ -43628,7 +43628,7 @@
       </c>
       <c r="X510" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="511" spans="1:24" x14ac:dyDescent="0.3">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="X511" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="512" spans="1:24" x14ac:dyDescent="0.3">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="X512" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="513" spans="1:24" x14ac:dyDescent="0.3">
@@ -43775,7 +43775,7 @@
       </c>
       <c r="X513" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="514" spans="1:24" x14ac:dyDescent="0.3">
@@ -43824,7 +43824,7 @@
       </c>
       <c r="X514" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="515" spans="1:24" x14ac:dyDescent="0.3">
@@ -43873,7 +43873,7 @@
       </c>
       <c r="X515" s="11">
         <f t="shared" ref="X515:X578" ca="1" si="8">W515-TODAY()</f>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="516" spans="1:24" x14ac:dyDescent="0.3">
@@ -43922,7 +43922,7 @@
       </c>
       <c r="X516" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="517" spans="1:24" x14ac:dyDescent="0.3">
@@ -43971,7 +43971,7 @@
       </c>
       <c r="X517" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>516</v>
+        <v>394</v>
       </c>
     </row>
     <row r="518" spans="1:24" x14ac:dyDescent="0.3">
@@ -44020,7 +44020,7 @@
       </c>
       <c r="X518" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>363</v>
+        <v>241</v>
       </c>
     </row>
     <row r="519" spans="1:24" x14ac:dyDescent="0.3">
@@ -44069,7 +44069,7 @@
       </c>
       <c r="X519" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="520" spans="1:24" x14ac:dyDescent="0.3">
@@ -44118,7 +44118,7 @@
       </c>
       <c r="X520" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="521" spans="1:24" x14ac:dyDescent="0.3">
@@ -44167,7 +44167,7 @@
       </c>
       <c r="X521" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="522" spans="1:24" x14ac:dyDescent="0.3">
@@ -44216,7 +44216,7 @@
       </c>
       <c r="X522" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="523" spans="1:24" x14ac:dyDescent="0.3">
@@ -44265,7 +44265,7 @@
       </c>
       <c r="X523" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="524" spans="1:24" x14ac:dyDescent="0.3">
@@ -44314,7 +44314,7 @@
       </c>
       <c r="X524" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="525" spans="1:24" x14ac:dyDescent="0.3">
@@ -44363,7 +44363,7 @@
       </c>
       <c r="X525" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="526" spans="1:24" x14ac:dyDescent="0.3">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="X526" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="527" spans="1:24" x14ac:dyDescent="0.3">
@@ -44461,7 +44461,7 @@
       </c>
       <c r="X527" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>516</v>
+        <v>394</v>
       </c>
     </row>
     <row r="528" spans="1:24" x14ac:dyDescent="0.3">
@@ -44510,7 +44510,7 @@
       </c>
       <c r="X528" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="529" spans="1:24" x14ac:dyDescent="0.3">
@@ -44559,7 +44559,7 @@
       </c>
       <c r="X529" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="530" spans="1:24" x14ac:dyDescent="0.3">
@@ -44608,7 +44608,7 @@
       </c>
       <c r="X530" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="531" spans="1:24" x14ac:dyDescent="0.3">
@@ -44657,7 +44657,7 @@
       </c>
       <c r="X531" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="532" spans="1:24" x14ac:dyDescent="0.3">
@@ -44706,7 +44706,7 @@
       </c>
       <c r="X532" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="533" spans="1:24" x14ac:dyDescent="0.3">
@@ -44755,7 +44755,7 @@
       </c>
       <c r="X533" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="534" spans="1:24" x14ac:dyDescent="0.3">
@@ -44804,7 +44804,7 @@
       </c>
       <c r="X534" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="535" spans="1:24" x14ac:dyDescent="0.3">
@@ -44853,7 +44853,7 @@
       </c>
       <c r="X535" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="536" spans="1:24" x14ac:dyDescent="0.3">
@@ -44902,7 +44902,7 @@
       </c>
       <c r="X536" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="537" spans="1:24" x14ac:dyDescent="0.3">
@@ -44951,7 +44951,7 @@
       </c>
       <c r="X537" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="538" spans="1:24" x14ac:dyDescent="0.3">
@@ -45000,7 +45000,7 @@
       </c>
       <c r="X538" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="539" spans="1:24" x14ac:dyDescent="0.3">
@@ -45049,7 +45049,7 @@
       </c>
       <c r="X539" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="540" spans="1:24" x14ac:dyDescent="0.3">
@@ -45101,7 +45101,7 @@
       </c>
       <c r="X540" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="541" spans="1:24" x14ac:dyDescent="0.3">
@@ -45150,7 +45150,7 @@
       </c>
       <c r="X541" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="542" spans="1:24" x14ac:dyDescent="0.3">
@@ -45199,7 +45199,7 @@
       </c>
       <c r="X542" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="543" spans="1:24" x14ac:dyDescent="0.3">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="X543" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="544" spans="1:24" x14ac:dyDescent="0.3">
@@ -45304,7 +45304,7 @@
       </c>
       <c r="X544" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="545" spans="1:118" x14ac:dyDescent="0.3">
@@ -45360,7 +45360,7 @@
       </c>
       <c r="X545" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="546" spans="1:118" x14ac:dyDescent="0.3">
@@ -45409,7 +45409,7 @@
       </c>
       <c r="X546" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
       <c r="Y546" s="4"/>
       <c r="Z546" s="4"/>
@@ -45552,7 +45552,7 @@
       </c>
       <c r="X547" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="548" spans="1:118" x14ac:dyDescent="0.3">
@@ -45601,7 +45601,7 @@
       </c>
       <c r="X548" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="Y548" s="4"/>
       <c r="Z548" s="4"/>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="X549" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="550" spans="1:118" x14ac:dyDescent="0.3">
@@ -45793,7 +45793,7 @@
       </c>
       <c r="X550" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="551" spans="1:118" x14ac:dyDescent="0.3">
@@ -45842,7 +45842,7 @@
       </c>
       <c r="X551" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="552" spans="1:118" x14ac:dyDescent="0.3">
@@ -45891,7 +45891,7 @@
       </c>
       <c r="X552" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="553" spans="1:118" x14ac:dyDescent="0.3">
@@ -45940,7 +45940,7 @@
       </c>
       <c r="X553" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="554" spans="1:118" x14ac:dyDescent="0.3">
@@ -45989,7 +45989,7 @@
       </c>
       <c r="X554" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="555" spans="1:118" x14ac:dyDescent="0.3">
@@ -46038,7 +46038,7 @@
       </c>
       <c r="X555" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="556" spans="1:118" x14ac:dyDescent="0.3">
@@ -46087,7 +46087,7 @@
       </c>
       <c r="X556" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="557" spans="1:118" x14ac:dyDescent="0.3">
@@ -46136,7 +46136,7 @@
       </c>
       <c r="X557" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="558" spans="1:118" x14ac:dyDescent="0.3">
@@ -46185,7 +46185,7 @@
       </c>
       <c r="X558" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="559" spans="1:118" x14ac:dyDescent="0.3">
@@ -46234,7 +46234,7 @@
       </c>
       <c r="X559" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="560" spans="1:118" x14ac:dyDescent="0.3">
@@ -46283,7 +46283,7 @@
       </c>
       <c r="X560" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="561" spans="1:24" x14ac:dyDescent="0.3">
@@ -46332,7 +46332,7 @@
       </c>
       <c r="X561" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="562" spans="1:24" x14ac:dyDescent="0.3">
@@ -46384,7 +46384,7 @@
       </c>
       <c r="X562" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="563" spans="1:24" x14ac:dyDescent="0.3">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="X563" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="564" spans="1:24" x14ac:dyDescent="0.3">
@@ -46482,7 +46482,7 @@
       </c>
       <c r="X564" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="565" spans="1:24" x14ac:dyDescent="0.3">
@@ -46531,7 +46531,7 @@
       </c>
       <c r="X565" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="566" spans="1:24" x14ac:dyDescent="0.3">
@@ -46580,7 +46580,7 @@
       </c>
       <c r="X566" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="567" spans="1:24" x14ac:dyDescent="0.3">
@@ -46632,7 +46632,7 @@
       </c>
       <c r="X567" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="568" spans="1:24" x14ac:dyDescent="0.3">
@@ -46681,7 +46681,7 @@
       </c>
       <c r="X568" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="569" spans="1:24" x14ac:dyDescent="0.3">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="X569" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="570" spans="1:24" x14ac:dyDescent="0.3">
@@ -46782,7 +46782,7 @@
       </c>
       <c r="X570" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>271</v>
+        <v>149</v>
       </c>
     </row>
     <row r="571" spans="1:24" x14ac:dyDescent="0.3">
@@ -46834,7 +46834,7 @@
       </c>
       <c r="X571" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="572" spans="1:24" x14ac:dyDescent="0.3">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="X572" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="573" spans="1:24" x14ac:dyDescent="0.3">
@@ -46932,7 +46932,7 @@
       </c>
       <c r="X573" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="574" spans="1:24" x14ac:dyDescent="0.3">
@@ -46981,7 +46981,7 @@
       </c>
       <c r="X574" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="575" spans="1:24" x14ac:dyDescent="0.3">
@@ -47030,7 +47030,7 @@
       </c>
       <c r="X575" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="576" spans="1:24" x14ac:dyDescent="0.3">
@@ -47082,7 +47082,7 @@
       </c>
       <c r="X576" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="577" spans="1:118" x14ac:dyDescent="0.3">
@@ -47131,7 +47131,7 @@
       </c>
       <c r="X577" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="578" spans="1:118" x14ac:dyDescent="0.3">
@@ -47180,7 +47180,7 @@
       </c>
       <c r="X578" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="579" spans="1:118" x14ac:dyDescent="0.3">
@@ -47229,7 +47229,7 @@
       </c>
       <c r="X579" s="11">
         <f t="shared" ref="X579:X625" ca="1" si="9">W579-TODAY()</f>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="580" spans="1:118" x14ac:dyDescent="0.3">
@@ -47278,7 +47278,7 @@
       </c>
       <c r="X580" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="581" spans="1:118" x14ac:dyDescent="0.3">
@@ -47327,7 +47327,7 @@
       </c>
       <c r="X581" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="582" spans="1:118" x14ac:dyDescent="0.3">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="X582" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="583" spans="1:118" x14ac:dyDescent="0.3">
@@ -47432,7 +47432,7 @@
       </c>
       <c r="X583" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="584" spans="1:118" x14ac:dyDescent="0.3">
@@ -47481,7 +47481,7 @@
       </c>
       <c r="X584" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="585" spans="1:118" x14ac:dyDescent="0.3">
@@ -47530,7 +47530,7 @@
       </c>
       <c r="X585" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="586" spans="1:118" x14ac:dyDescent="0.3">
@@ -47579,7 +47579,7 @@
       </c>
       <c r="X586" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="587" spans="1:118" x14ac:dyDescent="0.3">
@@ -47628,7 +47628,7 @@
       </c>
       <c r="X587" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="588" spans="1:118" x14ac:dyDescent="0.3">
@@ -47680,7 +47680,7 @@
       </c>
       <c r="X588" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
       <c r="Y588" s="4"/>
       <c r="Z588" s="4"/>
@@ -47820,7 +47820,7 @@
       </c>
       <c r="X589" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="590" spans="1:118" x14ac:dyDescent="0.3">
@@ -47869,7 +47869,7 @@
       </c>
       <c r="X590" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="591" spans="1:118" x14ac:dyDescent="0.3">
@@ -47918,7 +47918,7 @@
       </c>
       <c r="X591" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>212</v>
+        <v>90</v>
       </c>
     </row>
     <row r="592" spans="1:118" x14ac:dyDescent="0.3">
@@ -47967,7 +47967,7 @@
       </c>
       <c r="X592" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="593" spans="1:24" x14ac:dyDescent="0.3">
@@ -48019,7 +48019,7 @@
       </c>
       <c r="X593" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>393</v>
+        <v>271</v>
       </c>
     </row>
     <row r="594" spans="1:24" x14ac:dyDescent="0.3">
@@ -48068,7 +48068,7 @@
       </c>
       <c r="X594" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="595" spans="1:24" x14ac:dyDescent="0.3">
@@ -48117,7 +48117,7 @@
       </c>
       <c r="X595" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="596" spans="1:24" x14ac:dyDescent="0.3">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="X596" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="597" spans="1:24" x14ac:dyDescent="0.3">
@@ -48224,7 +48224,7 @@
       </c>
       <c r="X597" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="598" spans="1:24" x14ac:dyDescent="0.3">
@@ -48273,7 +48273,7 @@
       </c>
       <c r="X598" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="599" spans="1:24" x14ac:dyDescent="0.3">
@@ -48322,7 +48322,7 @@
       </c>
       <c r="X599" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="600" spans="1:24" x14ac:dyDescent="0.3">
@@ -48371,7 +48371,7 @@
       </c>
       <c r="X600" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="601" spans="1:24" x14ac:dyDescent="0.3">
@@ -48420,7 +48420,7 @@
       </c>
       <c r="X601" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="602" spans="1:24" x14ac:dyDescent="0.3">
@@ -48469,7 +48469,7 @@
       </c>
       <c r="X602" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>363</v>
+        <v>241</v>
       </c>
     </row>
     <row r="603" spans="1:24" x14ac:dyDescent="0.3">
@@ -48518,7 +48518,7 @@
       </c>
       <c r="X603" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>59</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="604" spans="1:24" x14ac:dyDescent="0.3">
@@ -48567,7 +48567,7 @@
       </c>
       <c r="X604" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="605" spans="1:24" x14ac:dyDescent="0.3">
@@ -48616,7 +48616,7 @@
       </c>
       <c r="X605" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="606" spans="1:24" x14ac:dyDescent="0.3">
@@ -48665,7 +48665,7 @@
       </c>
       <c r="X606" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="607" spans="1:24" x14ac:dyDescent="0.3">
@@ -48714,7 +48714,7 @@
       </c>
       <c r="X607" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="608" spans="1:24" x14ac:dyDescent="0.3">
@@ -48763,7 +48763,7 @@
       </c>
       <c r="X608" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="609" spans="1:24" x14ac:dyDescent="0.3">
@@ -48812,7 +48812,7 @@
       </c>
       <c r="X609" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="610" spans="1:24" x14ac:dyDescent="0.3">
@@ -48861,7 +48861,7 @@
       </c>
       <c r="X610" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="611" spans="1:24" x14ac:dyDescent="0.3">
@@ -48910,7 +48910,7 @@
       </c>
       <c r="X611" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="612" spans="1:24" x14ac:dyDescent="0.3">
@@ -48959,7 +48959,7 @@
       </c>
       <c r="X612" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="613" spans="1:24" x14ac:dyDescent="0.3">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="X613" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-33</v>
+        <v>-155</v>
       </c>
     </row>
     <row r="614" spans="1:24" x14ac:dyDescent="0.3">
@@ -49057,7 +49057,7 @@
       </c>
       <c r="X614" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>212</v>
+        <v>90</v>
       </c>
     </row>
     <row r="615" spans="1:24" x14ac:dyDescent="0.3">
@@ -49106,7 +49106,7 @@
       </c>
       <c r="X615" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="616" spans="1:24" x14ac:dyDescent="0.3">
@@ -49155,7 +49155,7 @@
       </c>
       <c r="X616" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="617" spans="1:24" x14ac:dyDescent="0.3">
@@ -49201,7 +49201,7 @@
       </c>
       <c r="X617" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="618" spans="1:24" x14ac:dyDescent="0.3">
@@ -49250,7 +49250,7 @@
       </c>
       <c r="X618" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="619" spans="1:24" x14ac:dyDescent="0.3">
@@ -49299,7 +49299,7 @@
       </c>
       <c r="X619" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="620" spans="1:24" x14ac:dyDescent="0.3">
@@ -49348,7 +49348,7 @@
       </c>
       <c r="X620" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="621" spans="1:24" x14ac:dyDescent="0.3">
@@ -49397,7 +49397,7 @@
       </c>
       <c r="X621" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>151</v>
+        <v>29</v>
       </c>
     </row>
     <row r="622" spans="1:24" x14ac:dyDescent="0.3">
@@ -49443,7 +49443,7 @@
       </c>
       <c r="X622" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="623" spans="1:24" x14ac:dyDescent="0.3">
@@ -49489,7 +49489,7 @@
       </c>
       <c r="X623" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-459</v>
+        <v>-581</v>
       </c>
     </row>
     <row r="624" spans="1:24" x14ac:dyDescent="0.3">
@@ -49535,7 +49535,7 @@
       </c>
       <c r="X624" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-2</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="625" spans="1:24" x14ac:dyDescent="0.3">
@@ -49581,7 +49581,7 @@
       </c>
       <c r="X625" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>28</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="631" spans="1:24" x14ac:dyDescent="0.3">

--- a/Sindicatos Mediador.xlsx
+++ b/Sindicatos Mediador.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\165973\Desktop\Mediador\mediador exe V3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\172299\Desktop\teste mediador\mediador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E3B4B9-D000-4114-B124-F21920D6EB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72A2B5F-6F7D-41EB-AF76-71202314474E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BASE (CNPJ ÚNICOS)'!$A$1:$E$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SINDICATOS CONTRA'!$V$1:$V$633</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -11429,9 +11430,6 @@
     <t>Mambore</t>
   </si>
   <si>
-    <t>Nao Me Toque</t>
-  </si>
-  <si>
     <t>Herval d Oeste</t>
   </si>
   <si>
@@ -11709,6 +11707,9 @@
   </si>
   <si>
     <t>Data-base</t>
+  </si>
+  <si>
+    <t>Não-Me-Toque</t>
   </si>
 </sst>
 </file>
@@ -17716,16 +17717,16 @@
         <v>1153</v>
       </c>
       <c r="U1" s="50" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="V1" s="50" t="s">
+        <v>3671</v>
+      </c>
+      <c r="W1" s="50" t="s">
+        <v>3673</v>
+      </c>
+      <c r="X1" s="50" t="s">
         <v>3672</v>
-      </c>
-      <c r="W1" s="50" t="s">
-        <v>3674</v>
-      </c>
-      <c r="X1" s="50" t="s">
-        <v>3673</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -17789,7 +17790,7 @@
       </c>
       <c r="X2" s="11">
         <f ca="1">W2-TODAY()</f>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -17844,7 +17845,7 @@
       </c>
       <c r="X3" s="11">
         <f t="shared" ref="X3:X66" ca="1" si="0">W3-TODAY()</f>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -17910,7 +17911,7 @@
       </c>
       <c r="X4" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -17951,7 +17952,7 @@
         <v>1140</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V5" s="11" t="s">
         <v>2926</v>
@@ -17962,7 +17963,7 @@
       </c>
       <c r="X5" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
@@ -18023,7 +18024,7 @@
       </c>
       <c r="X6" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -18064,7 +18065,7 @@
         <v>1151</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="V7" s="11" t="s">
         <v>3151</v>
@@ -18075,7 +18076,7 @@
       </c>
       <c r="X7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -18136,7 +18137,7 @@
       </c>
       <c r="X8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -18197,7 +18198,7 @@
       </c>
       <c r="X9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
@@ -18238,7 +18239,7 @@
         <v>1140</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V10" s="11" t="s">
         <v>3397</v>
@@ -18249,7 +18250,7 @@
       </c>
       <c r="X10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
@@ -18290,7 +18291,7 @@
         <v>1140</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V11" s="11" t="s">
         <v>3398</v>
@@ -18301,7 +18302,7 @@
       </c>
       <c r="X11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -18342,7 +18343,7 @@
         <v>1142</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="V12" s="11" t="s">
         <v>2945</v>
@@ -18353,7 +18354,7 @@
       </c>
       <c r="X12" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -18405,7 +18406,7 @@
       </c>
       <c r="X13" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -18466,7 +18467,7 @@
       </c>
       <c r="X14" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
@@ -18518,7 +18519,7 @@
       </c>
       <c r="X15" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
@@ -18559,7 +18560,7 @@
         <v>1142</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="V16" s="11" t="s">
         <v>3400</v>
@@ -18570,7 +18571,7 @@
       </c>
       <c r="X16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
@@ -18622,7 +18623,7 @@
       </c>
       <c r="X17" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
@@ -18660,7 +18661,7 @@
         <v>1172</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>2937</v>
@@ -18671,7 +18672,7 @@
       </c>
       <c r="X18" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-520</v>
+        <v>-671</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -18712,7 +18713,7 @@
         <v>1142</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="V19" s="11" t="s">
         <v>3264</v>
@@ -18723,7 +18724,7 @@
       </c>
       <c r="X19" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -18775,7 +18776,7 @@
       </c>
       <c r="X20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
@@ -18836,7 +18837,7 @@
       </c>
       <c r="X21" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -18877,7 +18878,7 @@
         <v>1151</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="V22" s="11" t="s">
         <v>3403</v>
@@ -18888,7 +18889,7 @@
       </c>
       <c r="X22" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -18940,7 +18941,7 @@
       </c>
       <c r="X23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -18981,7 +18982,7 @@
         <v>1140</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V24" s="11" t="s">
         <v>3405</v>
@@ -18992,7 +18993,7 @@
       </c>
       <c r="X24" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -19033,7 +19034,7 @@
         <v>1158</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="V25" s="11" t="s">
         <v>3406</v>
@@ -19044,7 +19045,7 @@
       </c>
       <c r="X25" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
@@ -19096,7 +19097,7 @@
       </c>
       <c r="X26" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -19137,7 +19138,7 @@
         <v>698</v>
       </c>
       <c r="V27" s="18" t="s">
-        <v>3581</v>
+        <v>3674</v>
       </c>
       <c r="W27" s="54">
         <f>INDEX([1]ACOMPANHAMENTO!H:H,MATCH(A27,[1]ACOMPANHAMENTO!A:A,0))</f>
@@ -19145,7 +19146,7 @@
       </c>
       <c r="X27" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -19186,7 +19187,7 @@
         <v>1140</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V28" s="11" t="s">
         <v>3407</v>
@@ -19197,7 +19198,7 @@
       </c>
       <c r="X28" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -19249,7 +19250,7 @@
       </c>
       <c r="X29" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -19298,7 +19299,7 @@
       </c>
       <c r="X30" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-886</v>
+        <v>-1037</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -19359,7 +19360,7 @@
       </c>
       <c r="X31" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -19408,7 +19409,7 @@
       </c>
       <c r="X32" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-520</v>
+        <v>-671</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
@@ -19460,7 +19461,7 @@
       </c>
       <c r="X33" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
@@ -19512,7 +19513,7 @@
       </c>
       <c r="X34" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
@@ -19559,7 +19560,7 @@
       </c>
       <c r="X35" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-947</v>
+        <v>-1098</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
@@ -19611,7 +19612,7 @@
       </c>
       <c r="X36" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
@@ -19660,7 +19661,7 @@
       </c>
       <c r="X37" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
@@ -19712,7 +19713,7 @@
       </c>
       <c r="X38" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
@@ -19764,7 +19765,7 @@
       </c>
       <c r="X39" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
@@ -19816,7 +19817,7 @@
       </c>
       <c r="X40" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
@@ -19868,7 +19869,7 @@
       </c>
       <c r="X41" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
@@ -19909,7 +19910,7 @@
         <v>1140</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V42" s="11" t="s">
         <v>3405</v>
@@ -19920,7 +19921,7 @@
       </c>
       <c r="X42" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
@@ -19972,7 +19973,7 @@
       </c>
       <c r="X43" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
@@ -20021,7 +20022,7 @@
       </c>
       <c r="X44" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
@@ -20062,7 +20063,7 @@
         <v>1183</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="V45" s="11" t="s">
         <v>3190</v>
@@ -20073,7 +20074,7 @@
       </c>
       <c r="X45" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
@@ -20114,7 +20115,7 @@
         <v>1185</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="V46" s="11" t="s">
         <v>3413</v>
@@ -20125,7 +20126,7 @@
       </c>
       <c r="X46" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-550</v>
+        <v>-701</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
@@ -20166,7 +20167,7 @@
         <v>1172</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="V47" s="11" t="s">
         <v>3414</v>
@@ -20177,7 +20178,7 @@
       </c>
       <c r="X47" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
@@ -20229,7 +20230,7 @@
       </c>
       <c r="X48" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
@@ -20284,7 +20285,7 @@
       </c>
       <c r="X49" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
@@ -20336,7 +20337,7 @@
       </c>
       <c r="X50" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
@@ -20388,7 +20389,7 @@
       </c>
       <c r="X51" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
@@ -20440,7 +20441,7 @@
       </c>
       <c r="X52" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
@@ -20492,7 +20493,7 @@
       </c>
       <c r="X53" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
@@ -20544,7 +20545,7 @@
       </c>
       <c r="X54" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
@@ -20585,7 +20586,7 @@
         <v>1151</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="V55" s="11" t="s">
         <v>2878</v>
@@ -20596,7 +20597,7 @@
       </c>
       <c r="X55" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
@@ -20648,7 +20649,7 @@
       </c>
       <c r="X56" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
@@ -20700,7 +20701,7 @@
       </c>
       <c r="X57" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
@@ -20741,7 +20742,7 @@
         <v>1183</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="V58" s="11" t="s">
         <v>3190</v>
@@ -20752,7 +20753,7 @@
       </c>
       <c r="X58" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
@@ -20804,7 +20805,7 @@
       </c>
       <c r="X59" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
@@ -20865,7 +20866,7 @@
       </c>
       <c r="X60" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
@@ -20919,7 +20920,7 @@
       </c>
       <c r="X61" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
@@ -20971,7 +20972,7 @@
       </c>
       <c r="X62" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
@@ -21026,7 +21027,7 @@
       </c>
       <c r="X63" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
@@ -21067,7 +21068,7 @@
         <v>1201</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V64" s="11" t="s">
         <v>3127</v>
@@ -21078,7 +21079,7 @@
       </c>
       <c r="X64" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.3">
@@ -21134,7 +21135,7 @@
       </c>
       <c r="X65" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.3">
@@ -21186,7 +21187,7 @@
       </c>
       <c r="X66" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.3">
@@ -21227,7 +21228,7 @@
         <v>1205</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="V67" s="11" t="s">
         <v>3419</v>
@@ -21238,7 +21239,7 @@
       </c>
       <c r="X67" s="11">
         <f t="shared" ref="X67:X130" ca="1" si="1">W67-TODAY()</f>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.3">
@@ -21290,7 +21291,7 @@
       </c>
       <c r="X68" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.3">
@@ -21345,7 +21346,7 @@
       </c>
       <c r="X69" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.3">
@@ -21397,7 +21398,7 @@
       </c>
       <c r="X70" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.3">
@@ -21438,7 +21439,7 @@
         <v>1201</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V71" s="11" t="s">
         <v>3066</v>
@@ -21449,7 +21450,7 @@
       </c>
       <c r="X71" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.3">
@@ -21501,7 +21502,7 @@
       </c>
       <c r="X72" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.3">
@@ -21548,7 +21549,7 @@
       </c>
       <c r="X73" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-610</v>
+        <v>-761</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.3">
@@ -21600,7 +21601,7 @@
       </c>
       <c r="X74" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.3">
@@ -21652,7 +21653,7 @@
       </c>
       <c r="X75" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.3">
@@ -21693,7 +21694,7 @@
         <v>1215</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="V76" s="11" t="s">
         <v>3260</v>
@@ -21704,7 +21705,7 @@
       </c>
       <c r="X76" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.3">
@@ -21756,7 +21757,7 @@
       </c>
       <c r="X77" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.3">
@@ -21808,7 +21809,7 @@
       </c>
       <c r="X78" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.3">
@@ -21857,7 +21858,7 @@
       </c>
       <c r="X79" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>302</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
@@ -21909,7 +21910,7 @@
       </c>
       <c r="X80" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.3">
@@ -21961,7 +21962,7 @@
       </c>
       <c r="X81" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.3">
@@ -22013,7 +22014,7 @@
       </c>
       <c r="X82" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.3">
@@ -22065,7 +22066,7 @@
       </c>
       <c r="X83" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
@@ -22117,7 +22118,7 @@
       </c>
       <c r="X84" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.3">
@@ -22169,7 +22170,7 @@
       </c>
       <c r="X85" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.3">
@@ -22221,7 +22222,7 @@
       </c>
       <c r="X86" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.3">
@@ -22276,7 +22277,7 @@
       </c>
       <c r="X87" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.3">
@@ -22328,7 +22329,7 @@
       </c>
       <c r="X88" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.3">
@@ -22380,7 +22381,7 @@
       </c>
       <c r="X89" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.3">
@@ -22432,7 +22433,7 @@
       </c>
       <c r="X90" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.3">
@@ -22484,7 +22485,7 @@
       </c>
       <c r="X91" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.3">
@@ -22536,7 +22537,7 @@
       </c>
       <c r="X92" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.3">
@@ -22588,7 +22589,7 @@
       </c>
       <c r="X93" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.3">
@@ -22640,7 +22641,7 @@
       </c>
       <c r="X94" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.3">
@@ -22692,7 +22693,7 @@
       </c>
       <c r="X95" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.3">
@@ -22744,7 +22745,7 @@
       </c>
       <c r="X96" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.3">
@@ -22796,7 +22797,7 @@
       </c>
       <c r="X97" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.3">
@@ -22848,7 +22849,7 @@
       </c>
       <c r="X98" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.3">
@@ -22900,7 +22901,7 @@
       </c>
       <c r="X99" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
@@ -22952,7 +22953,7 @@
       </c>
       <c r="X100" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.3">
@@ -23004,7 +23005,7 @@
       </c>
       <c r="X101" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.3">
@@ -23045,7 +23046,7 @@
         <v>1250</v>
       </c>
       <c r="U102" s="11" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="V102" s="11" t="s">
         <v>2884</v>
@@ -23056,7 +23057,7 @@
       </c>
       <c r="X102" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
@@ -23108,7 +23109,7 @@
       </c>
       <c r="X103" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.3">
@@ -23149,7 +23150,7 @@
         <v>1201</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V104" s="11" t="s">
         <v>3127</v>
@@ -23160,7 +23161,7 @@
       </c>
       <c r="X104" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.3">
@@ -23209,7 +23210,7 @@
       </c>
       <c r="X105" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
@@ -23261,7 +23262,7 @@
       </c>
       <c r="X106" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.3">
@@ -23313,7 +23314,7 @@
       </c>
       <c r="X107" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.3">
@@ -23365,7 +23366,7 @@
       </c>
       <c r="X108" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.3">
@@ -23417,7 +23418,7 @@
       </c>
       <c r="X109" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.3">
@@ -23469,7 +23470,7 @@
       </c>
       <c r="X110" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
@@ -23521,7 +23522,7 @@
       </c>
       <c r="X111" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.3">
@@ -23559,7 +23560,7 @@
         <v>1259</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="V112" s="11" t="s">
         <v>3104</v>
@@ -23570,7 +23571,7 @@
       </c>
       <c r="X112" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
@@ -23608,7 +23609,7 @@
         <v>1259</v>
       </c>
       <c r="U113" s="11" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="V113" s="11" t="s">
         <v>3095</v>
@@ -23619,7 +23620,7 @@
       </c>
       <c r="X113" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
@@ -23671,7 +23672,7 @@
       </c>
       <c r="X114" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.3">
@@ -23709,7 +23710,7 @@
         <v>1264</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="V115" s="11" t="s">
         <v>3438</v>
@@ -23720,7 +23721,7 @@
       </c>
       <c r="X115" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
@@ -23772,7 +23773,7 @@
       </c>
       <c r="X116" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.3">
@@ -23810,7 +23811,7 @@
         <v>1264</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="V117" s="11" t="s">
         <v>3439</v>
@@ -23821,7 +23822,7 @@
       </c>
       <c r="X117" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
@@ -23870,7 +23871,7 @@
       </c>
       <c r="X118" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.3">
@@ -23922,7 +23923,7 @@
       </c>
       <c r="X119" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.3">
@@ -23974,7 +23975,7 @@
       </c>
       <c r="X120" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.3">
@@ -24026,7 +24027,7 @@
       </c>
       <c r="X121" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.3">
@@ -24075,7 +24076,7 @@
       </c>
       <c r="X122" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.3">
@@ -24122,7 +24123,7 @@
       </c>
       <c r="X123" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.3">
@@ -24171,7 +24172,7 @@
       </c>
       <c r="X124" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.3">
@@ -24223,7 +24224,7 @@
       </c>
       <c r="X125" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.3">
@@ -24275,7 +24276,7 @@
       </c>
       <c r="X126" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.3">
@@ -24327,7 +24328,7 @@
       </c>
       <c r="X127" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.3">
@@ -24363,7 +24364,7 @@
         <v>1272</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V128" s="11" t="s">
         <v>3443</v>
@@ -24374,7 +24375,7 @@
       </c>
       <c r="X128" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-3138</v>
+        <v>-3289</v>
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.3">
@@ -24412,7 +24413,7 @@
         <v>1272</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V129" s="11" t="s">
         <v>2928</v>
@@ -24423,7 +24424,7 @@
       </c>
       <c r="X129" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-4234</v>
+        <v>-4385</v>
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.3">
@@ -24475,7 +24476,7 @@
       </c>
       <c r="X130" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.3">
@@ -24527,7 +24528,7 @@
       </c>
       <c r="X131" s="11">
         <f t="shared" ref="X131:X194" ca="1" si="2">W131-TODAY()</f>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.3">
@@ -24579,7 +24580,7 @@
       </c>
       <c r="X132" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.3">
@@ -24634,7 +24635,7 @@
       </c>
       <c r="X133" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.3">
@@ -24683,7 +24684,7 @@
       </c>
       <c r="X134" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.3">
@@ -24735,7 +24736,7 @@
       </c>
       <c r="X135" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.3">
@@ -24787,7 +24788,7 @@
       </c>
       <c r="X136" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.3">
@@ -24839,7 +24840,7 @@
       </c>
       <c r="X137" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.3">
@@ -24891,7 +24892,7 @@
       </c>
       <c r="X138" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.3">
@@ -24943,7 +24944,7 @@
       </c>
       <c r="X139" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.3">
@@ -24995,7 +24996,7 @@
       </c>
       <c r="X140" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.3">
@@ -25047,7 +25048,7 @@
       </c>
       <c r="X141" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.3">
@@ -25099,7 +25100,7 @@
       </c>
       <c r="X142" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.3">
@@ -25154,7 +25155,7 @@
       </c>
       <c r="X143" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.3">
@@ -25195,7 +25196,7 @@
         <v>1151</v>
       </c>
       <c r="U144" s="11" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="V144" s="11" t="s">
         <v>3448</v>
@@ -25206,7 +25207,7 @@
       </c>
       <c r="X144" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.3">
@@ -25258,7 +25259,7 @@
       </c>
       <c r="X145" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.3">
@@ -25307,7 +25308,7 @@
       </c>
       <c r="X146" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.3">
@@ -25359,7 +25360,7 @@
       </c>
       <c r="X147" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.3">
@@ -25411,7 +25412,7 @@
       </c>
       <c r="X148" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.3">
@@ -25472,7 +25473,7 @@
       </c>
       <c r="X149" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.3">
@@ -25524,7 +25525,7 @@
       </c>
       <c r="X150" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.3">
@@ -25576,7 +25577,7 @@
       </c>
       <c r="X151" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.3">
@@ -25628,7 +25629,7 @@
       </c>
       <c r="X152" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.3">
@@ -25680,7 +25681,7 @@
       </c>
       <c r="X153" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.3">
@@ -25729,7 +25730,7 @@
       </c>
       <c r="X154" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.3">
@@ -25781,7 +25782,7 @@
       </c>
       <c r="X155" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.3">
@@ -25833,7 +25834,7 @@
       </c>
       <c r="X156" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.3">
@@ -25885,7 +25886,7 @@
       </c>
       <c r="X157" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.3">
@@ -25923,7 +25924,7 @@
         <v>1264</v>
       </c>
       <c r="U158" s="11" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="V158" s="11" t="s">
         <v>2902</v>
@@ -25934,7 +25935,7 @@
       </c>
       <c r="X158" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.3">
@@ -25975,7 +25976,7 @@
         <v>1140</v>
       </c>
       <c r="U159" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V159" s="11" t="s">
         <v>3174</v>
@@ -25986,7 +25987,7 @@
       </c>
       <c r="X159" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.3">
@@ -26038,7 +26039,7 @@
       </c>
       <c r="X160" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.3">
@@ -26090,7 +26091,7 @@
       </c>
       <c r="X161" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.3">
@@ -26131,7 +26132,7 @@
         <v>1205</v>
       </c>
       <c r="U162" s="11" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="V162" s="11" t="s">
         <v>3450</v>
@@ -26142,7 +26143,7 @@
       </c>
       <c r="X162" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.3">
@@ -26191,7 +26192,7 @@
       </c>
       <c r="X163" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>151</v>
       </c>
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.3">
@@ -26238,7 +26239,7 @@
       </c>
       <c r="X164" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-428</v>
+        <v>-579</v>
       </c>
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.3">
@@ -26279,7 +26280,7 @@
         <v>1299</v>
       </c>
       <c r="U165" s="11" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="V165" s="11" t="s">
         <v>3171</v>
@@ -26290,7 +26291,7 @@
       </c>
       <c r="X165" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="166" spans="1:24" x14ac:dyDescent="0.3">
@@ -26342,7 +26343,7 @@
       </c>
       <c r="X166" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="167" spans="1:24" x14ac:dyDescent="0.3">
@@ -26394,7 +26395,7 @@
       </c>
       <c r="X167" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="168" spans="1:24" x14ac:dyDescent="0.3">
@@ -26443,7 +26444,7 @@
       </c>
       <c r="X168" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>151</v>
       </c>
     </row>
     <row r="169" spans="1:24" x14ac:dyDescent="0.3">
@@ -26495,7 +26496,7 @@
       </c>
       <c r="X169" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="170" spans="1:24" x14ac:dyDescent="0.3">
@@ -26547,7 +26548,7 @@
       </c>
       <c r="X170" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="171" spans="1:24" x14ac:dyDescent="0.3">
@@ -26599,7 +26600,7 @@
       </c>
       <c r="X171" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172" spans="1:24" x14ac:dyDescent="0.3">
@@ -26640,7 +26641,7 @@
         <v>1201</v>
       </c>
       <c r="U172" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V172" s="11" t="s">
         <v>3454</v>
@@ -26651,7 +26652,7 @@
       </c>
       <c r="X172" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="173" spans="1:24" x14ac:dyDescent="0.3">
@@ -26703,7 +26704,7 @@
       </c>
       <c r="X173" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="174" spans="1:24" x14ac:dyDescent="0.3">
@@ -26755,7 +26756,7 @@
       </c>
       <c r="X174" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="175" spans="1:24" x14ac:dyDescent="0.3">
@@ -26810,7 +26811,7 @@
       </c>
       <c r="X175" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="176" spans="1:24" x14ac:dyDescent="0.3">
@@ -26859,7 +26860,7 @@
       </c>
       <c r="X176" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.3">
@@ -26900,7 +26901,7 @@
         <v>1303</v>
       </c>
       <c r="U177" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V177" s="11" t="s">
         <v>2838</v>
@@ -26911,7 +26912,7 @@
       </c>
       <c r="X177" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.3">
@@ -26963,7 +26964,7 @@
       </c>
       <c r="X178" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="179" spans="1:24" x14ac:dyDescent="0.3">
@@ -27001,7 +27002,7 @@
         <v>1305</v>
       </c>
       <c r="U179" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V179" s="11" t="s">
         <v>2701</v>
@@ -27012,7 +27013,7 @@
       </c>
       <c r="X179" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="180" spans="1:24" x14ac:dyDescent="0.3">
@@ -27061,7 +27062,7 @@
       </c>
       <c r="X180" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="181" spans="1:24" x14ac:dyDescent="0.3">
@@ -27102,7 +27103,7 @@
         <v>1205</v>
       </c>
       <c r="U181" s="11" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="V181" s="11" t="s">
         <v>3023</v>
@@ -27113,7 +27114,7 @@
       </c>
       <c r="X181" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="182" spans="1:24" x14ac:dyDescent="0.3">
@@ -27168,7 +27169,7 @@
       </c>
       <c r="X182" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="183" spans="1:24" x14ac:dyDescent="0.3">
@@ -27215,7 +27216,7 @@
       </c>
       <c r="X183" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-610</v>
+        <v>-761</v>
       </c>
     </row>
     <row r="184" spans="1:24" x14ac:dyDescent="0.3">
@@ -27256,7 +27257,7 @@
         <v>1310</v>
       </c>
       <c r="U184" s="11" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="V184" s="11" t="s">
         <v>3255</v>
@@ -27267,7 +27268,7 @@
       </c>
       <c r="X184" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="185" spans="1:24" x14ac:dyDescent="0.3">
@@ -27308,7 +27309,7 @@
         <v>1310</v>
       </c>
       <c r="U185" s="11" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="V185" s="11" t="s">
         <v>2851</v>
@@ -27319,7 +27320,7 @@
       </c>
       <c r="X185" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="186" spans="1:24" x14ac:dyDescent="0.3">
@@ -27371,7 +27372,7 @@
       </c>
       <c r="X186" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="187" spans="1:24" x14ac:dyDescent="0.3">
@@ -27418,7 +27419,7 @@
       </c>
       <c r="X187" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-610</v>
+        <v>-761</v>
       </c>
     </row>
     <row r="188" spans="1:24" x14ac:dyDescent="0.3">
@@ -27467,7 +27468,7 @@
       </c>
       <c r="X188" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="189" spans="1:24" x14ac:dyDescent="0.3">
@@ -27516,7 +27517,7 @@
       </c>
       <c r="X189" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="190" spans="1:24" x14ac:dyDescent="0.3">
@@ -27554,7 +27555,7 @@
         <v>1272</v>
       </c>
       <c r="U190" s="11" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="V190" s="11" t="s">
         <v>2596</v>
@@ -27565,7 +27566,7 @@
       </c>
       <c r="X190" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="191" spans="1:24" x14ac:dyDescent="0.3">
@@ -27609,7 +27610,7 @@
         <v>1318</v>
       </c>
       <c r="U191" s="11" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="V191" s="11" t="s">
         <v>3053</v>
@@ -27620,7 +27621,7 @@
       </c>
       <c r="X191" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="192" spans="1:24" x14ac:dyDescent="0.3">
@@ -27661,7 +27662,7 @@
         <v>1201</v>
       </c>
       <c r="U192" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V192" s="11" t="s">
         <v>3127</v>
@@ -27672,7 +27673,7 @@
       </c>
       <c r="X192" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="193" spans="1:24" x14ac:dyDescent="0.3">
@@ -27721,7 +27722,7 @@
       </c>
       <c r="X193" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="194" spans="1:24" x14ac:dyDescent="0.3">
@@ -27773,7 +27774,7 @@
       </c>
       <c r="X194" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="195" spans="1:24" x14ac:dyDescent="0.3">
@@ -27822,7 +27823,7 @@
       </c>
       <c r="X195" s="11">
         <f t="shared" ref="X195:X258" ca="1" si="3">W195-TODAY()</f>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.3">
@@ -27874,7 +27875,7 @@
       </c>
       <c r="X196" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="197" spans="1:24" x14ac:dyDescent="0.3">
@@ -27912,7 +27913,7 @@
         <v>1259</v>
       </c>
       <c r="U197" s="11" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="V197" s="11" t="s">
         <v>3459</v>
@@ -27923,7 +27924,7 @@
       </c>
       <c r="X197" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="198" spans="1:24" x14ac:dyDescent="0.3">
@@ -27972,7 +27973,7 @@
       </c>
       <c r="X198" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="199" spans="1:24" x14ac:dyDescent="0.3">
@@ -28021,7 +28022,7 @@
       </c>
       <c r="X199" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="200" spans="1:24" x14ac:dyDescent="0.3">
@@ -28059,7 +28060,7 @@
         <v>1272</v>
       </c>
       <c r="U200" s="11" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="V200" s="11" t="s">
         <v>2604</v>
@@ -28070,7 +28071,7 @@
       </c>
       <c r="X200" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>90</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="201" spans="1:24" x14ac:dyDescent="0.3">
@@ -28119,7 +28120,7 @@
       </c>
       <c r="X201" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="202" spans="1:24" x14ac:dyDescent="0.3">
@@ -28168,7 +28169,7 @@
       </c>
       <c r="X202" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>90</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="203" spans="1:24" x14ac:dyDescent="0.3">
@@ -28217,7 +28218,7 @@
       </c>
       <c r="X203" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="204" spans="1:24" x14ac:dyDescent="0.3">
@@ -28266,7 +28267,7 @@
       </c>
       <c r="X204" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="205" spans="1:24" x14ac:dyDescent="0.3">
@@ -28315,7 +28316,7 @@
       </c>
       <c r="X205" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="206" spans="1:24" x14ac:dyDescent="0.3">
@@ -28364,7 +28365,7 @@
       </c>
       <c r="X206" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-520</v>
+        <v>-671</v>
       </c>
     </row>
     <row r="207" spans="1:24" x14ac:dyDescent="0.3">
@@ -28413,7 +28414,7 @@
       </c>
       <c r="X207" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>59</v>
       </c>
     </row>
     <row r="208" spans="1:24" x14ac:dyDescent="0.3">
@@ -28462,7 +28463,7 @@
       </c>
       <c r="X208" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="209" spans="1:24" x14ac:dyDescent="0.3">
@@ -28500,7 +28501,7 @@
         <v>1334</v>
       </c>
       <c r="U209" s="11" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="V209" s="11" t="s">
         <v>2637</v>
@@ -28511,7 +28512,7 @@
       </c>
       <c r="X209" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="210" spans="1:24" x14ac:dyDescent="0.3">
@@ -28569,7 +28570,7 @@
       </c>
       <c r="X210" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="211" spans="1:24" x14ac:dyDescent="0.3">
@@ -28618,7 +28619,7 @@
       </c>
       <c r="X211" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.3">
@@ -28667,7 +28668,7 @@
       </c>
       <c r="X212" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="213" spans="1:24" x14ac:dyDescent="0.3">
@@ -28716,7 +28717,7 @@
       </c>
       <c r="X213" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>59</v>
       </c>
     </row>
     <row r="214" spans="1:24" x14ac:dyDescent="0.3">
@@ -28765,7 +28766,7 @@
       </c>
       <c r="X214" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>59</v>
       </c>
     </row>
     <row r="215" spans="1:24" x14ac:dyDescent="0.3">
@@ -28803,7 +28804,7 @@
         <v>1336</v>
       </c>
       <c r="U215" s="11" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="V215" s="11" t="s">
         <v>2680</v>
@@ -28814,7 +28815,7 @@
       </c>
       <c r="X215" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="216" spans="1:24" x14ac:dyDescent="0.3">
@@ -28866,7 +28867,7 @@
       </c>
       <c r="X216" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="217" spans="1:24" x14ac:dyDescent="0.3">
@@ -28915,7 +28916,7 @@
       </c>
       <c r="X217" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="218" spans="1:24" x14ac:dyDescent="0.3">
@@ -28953,7 +28954,7 @@
         <v>1264</v>
       </c>
       <c r="U218" s="11" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="V218" s="11" t="s">
         <v>3005</v>
@@ -28964,7 +28965,7 @@
       </c>
       <c r="X218" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="219" spans="1:24" x14ac:dyDescent="0.3">
@@ -29005,7 +29006,7 @@
         <v>1338</v>
       </c>
       <c r="U219" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V219" s="11" t="s">
         <v>3147</v>
@@ -29016,7 +29017,7 @@
       </c>
       <c r="X219" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="220" spans="1:24" x14ac:dyDescent="0.3">
@@ -29068,7 +29069,7 @@
       </c>
       <c r="X220" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="221" spans="1:24" x14ac:dyDescent="0.3">
@@ -29120,7 +29121,7 @@
       </c>
       <c r="X221" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="222" spans="1:24" x14ac:dyDescent="0.3">
@@ -29161,7 +29162,7 @@
         <v>1185</v>
       </c>
       <c r="U222" s="11" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="V222" s="11" t="s">
         <v>3413</v>
@@ -29172,7 +29173,7 @@
       </c>
       <c r="X222" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-550</v>
+        <v>-701</v>
       </c>
     </row>
     <row r="223" spans="1:24" x14ac:dyDescent="0.3">
@@ -29213,7 +29214,7 @@
         <v>1338</v>
       </c>
       <c r="U223" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V223" s="11" t="s">
         <v>3147</v>
@@ -29224,7 +29225,7 @@
       </c>
       <c r="X223" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="224" spans="1:24" x14ac:dyDescent="0.3">
@@ -29265,7 +29266,7 @@
         <v>1338</v>
       </c>
       <c r="U224" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V224" s="11" t="s">
         <v>3147</v>
@@ -29276,7 +29277,7 @@
       </c>
       <c r="X224" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="225" spans="1:24" x14ac:dyDescent="0.3">
@@ -29317,7 +29318,7 @@
         <v>1338</v>
       </c>
       <c r="U225" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V225" s="11" t="s">
         <v>3147</v>
@@ -29328,7 +29329,7 @@
       </c>
       <c r="X225" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="226" spans="1:24" x14ac:dyDescent="0.3">
@@ -29375,7 +29376,7 @@
       </c>
       <c r="X226" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-428</v>
+        <v>-579</v>
       </c>
     </row>
     <row r="227" spans="1:24" x14ac:dyDescent="0.3">
@@ -29416,7 +29417,7 @@
         <v>1338</v>
       </c>
       <c r="U227" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V227" s="11" t="s">
         <v>3147</v>
@@ -29427,7 +29428,7 @@
       </c>
       <c r="X227" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="228" spans="1:24" x14ac:dyDescent="0.3">
@@ -29479,7 +29480,7 @@
       </c>
       <c r="X228" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="229" spans="1:24" x14ac:dyDescent="0.3">
@@ -29528,7 +29529,7 @@
       </c>
       <c r="X229" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>59</v>
       </c>
     </row>
     <row r="230" spans="1:24" x14ac:dyDescent="0.3">
@@ -29577,7 +29578,7 @@
       </c>
       <c r="X230" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="231" spans="1:24" x14ac:dyDescent="0.3">
@@ -29624,7 +29625,7 @@
       </c>
       <c r="X231" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="232" spans="1:24" x14ac:dyDescent="0.3">
@@ -29676,7 +29677,7 @@
       </c>
       <c r="X232" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="233" spans="1:24" x14ac:dyDescent="0.3">
@@ -29717,7 +29718,7 @@
         <v>1201</v>
       </c>
       <c r="U233" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V233" s="11" t="s">
         <v>2853</v>
@@ -29728,7 +29729,7 @@
       </c>
       <c r="X233" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="234" spans="1:24" x14ac:dyDescent="0.3">
@@ -29777,7 +29778,7 @@
       </c>
       <c r="X234" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="235" spans="1:24" x14ac:dyDescent="0.3">
@@ -29826,7 +29827,7 @@
       </c>
       <c r="X235" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="236" spans="1:24" x14ac:dyDescent="0.3">
@@ -29864,7 +29865,7 @@
         <v>1305</v>
       </c>
       <c r="U236" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V236" t="s">
         <v>3469</v>
@@ -29875,7 +29876,7 @@
       </c>
       <c r="X236" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="237" spans="1:24" x14ac:dyDescent="0.3">
@@ -29913,7 +29914,7 @@
         <v>1347</v>
       </c>
       <c r="U237" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="V237" t="s">
         <v>3470</v>
@@ -29924,7 +29925,7 @@
       </c>
       <c r="X237" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="238" spans="1:24" x14ac:dyDescent="0.3">
@@ -29976,7 +29977,7 @@
       </c>
       <c r="X238" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="239" spans="1:24" x14ac:dyDescent="0.3">
@@ -30028,7 +30029,7 @@
       </c>
       <c r="X239" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="240" spans="1:24" x14ac:dyDescent="0.3">
@@ -30080,7 +30081,7 @@
       </c>
       <c r="X240" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="241" spans="1:24" x14ac:dyDescent="0.3">
@@ -30129,7 +30130,7 @@
       </c>
       <c r="X241" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="242" spans="1:24" x14ac:dyDescent="0.3">
@@ -30167,7 +30168,7 @@
         <v>1349</v>
       </c>
       <c r="U242" s="11" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="V242" s="11" t="s">
         <v>2660</v>
@@ -30178,7 +30179,7 @@
       </c>
       <c r="X242" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="243" spans="1:24" x14ac:dyDescent="0.3">
@@ -30230,7 +30231,7 @@
       </c>
       <c r="X243" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="244" spans="1:24" x14ac:dyDescent="0.3">
@@ -30282,7 +30283,7 @@
       </c>
       <c r="X244" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="245" spans="1:24" x14ac:dyDescent="0.3">
@@ -30334,7 +30335,7 @@
       </c>
       <c r="X245" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="246" spans="1:24" x14ac:dyDescent="0.3">
@@ -30386,7 +30387,7 @@
       </c>
       <c r="X246" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="247" spans="1:24" x14ac:dyDescent="0.3">
@@ -30427,7 +30428,7 @@
         <v>1172</v>
       </c>
       <c r="U247" s="11" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="V247" s="11" t="s">
         <v>3414</v>
@@ -30438,7 +30439,7 @@
       </c>
       <c r="X247" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="248" spans="1:24" x14ac:dyDescent="0.3">
@@ -30499,7 +30500,7 @@
       </c>
       <c r="X248" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="249" spans="1:24" x14ac:dyDescent="0.3">
@@ -30548,7 +30549,7 @@
       </c>
       <c r="X249" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="250" spans="1:24" x14ac:dyDescent="0.3">
@@ -30597,7 +30598,7 @@
       </c>
       <c r="X250" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>59</v>
       </c>
     </row>
     <row r="251" spans="1:24" x14ac:dyDescent="0.3">
@@ -30649,7 +30650,7 @@
       </c>
       <c r="X251" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="252" spans="1:24" x14ac:dyDescent="0.3">
@@ -30701,7 +30702,7 @@
       </c>
       <c r="X252" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="253" spans="1:24" x14ac:dyDescent="0.3">
@@ -30753,7 +30754,7 @@
       </c>
       <c r="X253" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="254" spans="1:24" x14ac:dyDescent="0.3">
@@ -30791,7 +30792,7 @@
         <v>1347</v>
       </c>
       <c r="U254" s="11" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="V254" s="11" t="s">
         <v>2675</v>
@@ -30802,7 +30803,7 @@
       </c>
       <c r="X254" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="255" spans="1:24" x14ac:dyDescent="0.3">
@@ -30851,7 +30852,7 @@
       </c>
       <c r="X255" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="256" spans="1:24" x14ac:dyDescent="0.3">
@@ -30892,7 +30893,7 @@
         <v>1201</v>
       </c>
       <c r="U256" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V256" s="11" t="s">
         <v>3127</v>
@@ -30903,7 +30904,7 @@
       </c>
       <c r="X256" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="257" spans="1:24" x14ac:dyDescent="0.3">
@@ -30955,7 +30956,7 @@
       </c>
       <c r="X257" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="258" spans="1:24" x14ac:dyDescent="0.3">
@@ -31007,7 +31008,7 @@
       </c>
       <c r="X258" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="259" spans="1:24" x14ac:dyDescent="0.3">
@@ -31045,7 +31046,7 @@
         <v>1338</v>
       </c>
       <c r="U259" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V259" s="11" t="s">
         <v>3147</v>
@@ -31056,7 +31057,7 @@
       </c>
       <c r="X259" s="11">
         <f t="shared" ref="X259:X322" ca="1" si="4">W259-TODAY()</f>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="260" spans="1:24" x14ac:dyDescent="0.3">
@@ -31105,7 +31106,7 @@
       </c>
       <c r="X260" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>302</v>
+        <v>151</v>
       </c>
     </row>
     <row r="261" spans="1:24" x14ac:dyDescent="0.3">
@@ -31157,7 +31158,7 @@
       </c>
       <c r="X261" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="262" spans="1:24" x14ac:dyDescent="0.3">
@@ -31209,7 +31210,7 @@
       </c>
       <c r="X262" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="263" spans="1:24" x14ac:dyDescent="0.3">
@@ -31261,7 +31262,7 @@
       </c>
       <c r="X263" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="264" spans="1:24" x14ac:dyDescent="0.3">
@@ -31313,7 +31314,7 @@
       </c>
       <c r="X264" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="265" spans="1:24" x14ac:dyDescent="0.3">
@@ -31365,7 +31366,7 @@
       </c>
       <c r="X265" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="266" spans="1:24" x14ac:dyDescent="0.3">
@@ -31417,7 +31418,7 @@
       </c>
       <c r="X266" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-947</v>
+        <v>-1098</v>
       </c>
     </row>
     <row r="267" spans="1:24" x14ac:dyDescent="0.3">
@@ -31469,7 +31470,7 @@
       </c>
       <c r="X267" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="268" spans="1:24" x14ac:dyDescent="0.3">
@@ -31521,7 +31522,7 @@
       </c>
       <c r="X268" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="269" spans="1:24" x14ac:dyDescent="0.3">
@@ -31573,7 +31574,7 @@
       </c>
       <c r="X269" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="270" spans="1:24" x14ac:dyDescent="0.3">
@@ -31625,7 +31626,7 @@
       </c>
       <c r="X270" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="271" spans="1:24" x14ac:dyDescent="0.3">
@@ -31677,7 +31678,7 @@
       </c>
       <c r="X271" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="272" spans="1:24" x14ac:dyDescent="0.3">
@@ -31738,7 +31739,7 @@
       </c>
       <c r="X272" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="273" spans="1:24" x14ac:dyDescent="0.3">
@@ -31774,7 +31775,7 @@
         <v>1364</v>
       </c>
       <c r="U273" s="11" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="V273" s="11" t="s">
         <v>3472</v>
@@ -31785,7 +31786,7 @@
       </c>
       <c r="X273" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-3138</v>
+        <v>-3289</v>
       </c>
     </row>
     <row r="274" spans="1:24" x14ac:dyDescent="0.3">
@@ -31837,7 +31838,7 @@
       </c>
       <c r="X274" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="275" spans="1:24" x14ac:dyDescent="0.3">
@@ -31884,7 +31885,7 @@
         <v>1318</v>
       </c>
       <c r="U275" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="V275" t="s">
         <v>3473</v>
@@ -31895,7 +31896,7 @@
       </c>
       <c r="X275" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="276" spans="1:24" x14ac:dyDescent="0.3">
@@ -31936,7 +31937,7 @@
         <v>1140</v>
       </c>
       <c r="U276" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V276" t="s">
         <v>3474</v>
@@ -31947,7 +31948,7 @@
       </c>
       <c r="X276" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="277" spans="1:24" x14ac:dyDescent="0.3">
@@ -31988,7 +31989,7 @@
         <v>1303</v>
       </c>
       <c r="U277" s="11" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="V277" s="11" t="s">
         <v>2838</v>
@@ -31999,7 +32000,7 @@
       </c>
       <c r="X277" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="278" spans="1:24" x14ac:dyDescent="0.3">
@@ -32037,7 +32038,7 @@
         <v>1305</v>
       </c>
       <c r="U278" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V278" s="11" t="s">
         <v>3475</v>
@@ -32048,7 +32049,7 @@
       </c>
       <c r="X278" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="279" spans="1:24" x14ac:dyDescent="0.3">
@@ -32100,7 +32101,7 @@
       </c>
       <c r="X279" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="280" spans="1:24" x14ac:dyDescent="0.3">
@@ -32141,7 +32142,7 @@
         <v>1201</v>
       </c>
       <c r="U280" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V280" s="11" t="s">
         <v>3476</v>
@@ -32152,7 +32153,7 @@
       </c>
       <c r="X280" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="281" spans="1:24" x14ac:dyDescent="0.3">
@@ -32204,7 +32205,7 @@
       </c>
       <c r="X281" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="282" spans="1:24" x14ac:dyDescent="0.3">
@@ -32256,7 +32257,7 @@
       </c>
       <c r="X282" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="283" spans="1:24" x14ac:dyDescent="0.3">
@@ -32305,7 +32306,7 @@
       </c>
       <c r="X283" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="284" spans="1:24" x14ac:dyDescent="0.3">
@@ -32346,7 +32347,7 @@
         <v>1140</v>
       </c>
       <c r="U284" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V284" t="s">
         <v>3477</v>
@@ -32357,7 +32358,7 @@
       </c>
       <c r="X284" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="285" spans="1:24" x14ac:dyDescent="0.3">
@@ -32398,7 +32399,7 @@
         <v>1201</v>
       </c>
       <c r="U285" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V285" s="11" t="s">
         <v>3127</v>
@@ -32409,7 +32410,7 @@
       </c>
       <c r="X285" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="286" spans="1:24" x14ac:dyDescent="0.3">
@@ -32458,7 +32459,7 @@
       </c>
       <c r="X286" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="287" spans="1:24" x14ac:dyDescent="0.3">
@@ -32507,7 +32508,7 @@
       </c>
       <c r="X287" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="288" spans="1:24" x14ac:dyDescent="0.3">
@@ -32556,7 +32557,7 @@
       </c>
       <c r="X288" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="289" spans="1:24" x14ac:dyDescent="0.3">
@@ -32605,7 +32606,7 @@
       </c>
       <c r="X289" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="290" spans="1:24" x14ac:dyDescent="0.3">
@@ -32654,7 +32655,7 @@
       </c>
       <c r="X290" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="291" spans="1:24" x14ac:dyDescent="0.3">
@@ -32706,7 +32707,7 @@
       </c>
       <c r="X291" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="292" spans="1:24" x14ac:dyDescent="0.3">
@@ -32758,7 +32759,7 @@
       </c>
       <c r="X292" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="293" spans="1:24" x14ac:dyDescent="0.3">
@@ -32810,7 +32811,7 @@
       </c>
       <c r="X293" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="294" spans="1:24" x14ac:dyDescent="0.3">
@@ -32862,7 +32863,7 @@
       </c>
       <c r="X294" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="295" spans="1:24" x14ac:dyDescent="0.3">
@@ -32911,7 +32912,7 @@
       </c>
       <c r="X295" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="296" spans="1:24" x14ac:dyDescent="0.3">
@@ -32963,7 +32964,7 @@
       </c>
       <c r="X296" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="297" spans="1:24" x14ac:dyDescent="0.3">
@@ -33001,7 +33002,7 @@
         <v>1365</v>
       </c>
       <c r="U297" s="11" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="V297" s="11" t="s">
         <v>3481</v>
@@ -33012,7 +33013,7 @@
       </c>
       <c r="X297" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="298" spans="1:24" x14ac:dyDescent="0.3">
@@ -33064,7 +33065,7 @@
       </c>
       <c r="X298" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="299" spans="1:24" x14ac:dyDescent="0.3">
@@ -33113,7 +33114,7 @@
       </c>
       <c r="X299" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="300" spans="1:24" x14ac:dyDescent="0.3">
@@ -33165,7 +33166,7 @@
       </c>
       <c r="X300" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="301" spans="1:24" x14ac:dyDescent="0.3">
@@ -33212,7 +33213,7 @@
       </c>
       <c r="X301" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-610</v>
+        <v>-761</v>
       </c>
     </row>
     <row r="302" spans="1:24" x14ac:dyDescent="0.3">
@@ -33250,7 +33251,7 @@
         <v>1368</v>
       </c>
       <c r="U302" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V302" s="11" t="s">
         <v>3483</v>
@@ -33261,7 +33262,7 @@
       </c>
       <c r="X302" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="303" spans="1:24" x14ac:dyDescent="0.3">
@@ -33313,7 +33314,7 @@
       </c>
       <c r="X303" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="304" spans="1:24" x14ac:dyDescent="0.3">
@@ -33365,7 +33366,7 @@
       </c>
       <c r="X304" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="305" spans="1:24" x14ac:dyDescent="0.3">
@@ -33403,7 +33404,7 @@
         <v>1370</v>
       </c>
       <c r="U305" s="11" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="V305" s="11" t="s">
         <v>3484</v>
@@ -33414,7 +33415,7 @@
       </c>
       <c r="X305" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="306" spans="1:24" x14ac:dyDescent="0.3">
@@ -33469,7 +33470,7 @@
       </c>
       <c r="X306" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="307" spans="1:24" x14ac:dyDescent="0.3">
@@ -33510,7 +33511,7 @@
         <v>1183</v>
       </c>
       <c r="U307" s="11" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="V307" s="11" t="s">
         <v>3190</v>
@@ -33521,7 +33522,7 @@
       </c>
       <c r="X307" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="308" spans="1:24" x14ac:dyDescent="0.3">
@@ -33570,7 +33571,7 @@
       </c>
       <c r="X308" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="309" spans="1:24" x14ac:dyDescent="0.3">
@@ -33622,7 +33623,7 @@
       </c>
       <c r="X309" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="310" spans="1:24" x14ac:dyDescent="0.3">
@@ -33671,7 +33672,7 @@
       </c>
       <c r="X310" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="311" spans="1:24" x14ac:dyDescent="0.3">
@@ -33726,7 +33727,7 @@
       </c>
       <c r="X311" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="312" spans="1:24" x14ac:dyDescent="0.3">
@@ -33775,7 +33776,7 @@
       </c>
       <c r="X312" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="313" spans="1:24" x14ac:dyDescent="0.3">
@@ -33824,7 +33825,7 @@
       </c>
       <c r="X313" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="314" spans="1:24" x14ac:dyDescent="0.3">
@@ -33873,7 +33874,7 @@
       </c>
       <c r="X314" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="315" spans="1:24" x14ac:dyDescent="0.3">
@@ -33911,7 +33912,7 @@
         <v>1259</v>
       </c>
       <c r="U315" s="11" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="V315" s="11" t="s">
         <v>3488</v>
@@ -33922,7 +33923,7 @@
       </c>
       <c r="X315" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="316" spans="1:24" x14ac:dyDescent="0.3">
@@ -33971,7 +33972,7 @@
       </c>
       <c r="X316" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="317" spans="1:24" x14ac:dyDescent="0.3">
@@ -34020,7 +34021,7 @@
       </c>
       <c r="X317" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="318" spans="1:24" x14ac:dyDescent="0.3">
@@ -34067,7 +34068,7 @@
       </c>
       <c r="X318" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="319" spans="1:24" x14ac:dyDescent="0.3">
@@ -34116,7 +34117,7 @@
       </c>
       <c r="X319" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>210</v>
+        <v>59</v>
       </c>
     </row>
     <row r="320" spans="1:24" x14ac:dyDescent="0.3">
@@ -34168,7 +34169,7 @@
       </c>
       <c r="X320" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="321" spans="1:24" x14ac:dyDescent="0.3">
@@ -34215,7 +34216,7 @@
       </c>
       <c r="X321" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-610</v>
+        <v>-761</v>
       </c>
     </row>
     <row r="322" spans="1:24" x14ac:dyDescent="0.3">
@@ -34264,7 +34265,7 @@
       </c>
       <c r="X322" s="11">
         <f t="shared" ca="1" si="4"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="323" spans="1:24" x14ac:dyDescent="0.3">
@@ -34313,7 +34314,7 @@
       </c>
       <c r="X323" s="11">
         <f t="shared" ref="X323:X386" ca="1" si="5">W323-TODAY()</f>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="324" spans="1:24" x14ac:dyDescent="0.3">
@@ -34362,7 +34363,7 @@
       </c>
       <c r="X324" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="325" spans="1:24" x14ac:dyDescent="0.3">
@@ -34400,7 +34401,7 @@
         <v>1347</v>
       </c>
       <c r="U325" s="11" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="V325" s="11" t="s">
         <v>2744</v>
@@ -34411,7 +34412,7 @@
       </c>
       <c r="X325" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="326" spans="1:24" x14ac:dyDescent="0.3">
@@ -34452,7 +34453,7 @@
         <v>1140</v>
       </c>
       <c r="U326" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V326" s="11" t="s">
         <v>3490</v>
@@ -34463,7 +34464,7 @@
       </c>
       <c r="X326" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="327" spans="1:24" x14ac:dyDescent="0.3">
@@ -34512,7 +34513,7 @@
       </c>
       <c r="X327" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="328" spans="1:24" x14ac:dyDescent="0.3">
@@ -34561,7 +34562,7 @@
       </c>
       <c r="X328" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="329" spans="1:24" x14ac:dyDescent="0.3">
@@ -34599,7 +34600,7 @@
         <v>1347</v>
       </c>
       <c r="U329" s="11" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="V329" s="11" t="s">
         <v>2754</v>
@@ -34610,7 +34611,7 @@
       </c>
       <c r="X329" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="330" spans="1:24" x14ac:dyDescent="0.3">
@@ -34659,7 +34660,7 @@
       </c>
       <c r="X330" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="331" spans="1:24" x14ac:dyDescent="0.3">
@@ -34708,7 +34709,7 @@
       </c>
       <c r="X331" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="332" spans="1:24" x14ac:dyDescent="0.3">
@@ -34746,7 +34747,7 @@
         <v>1379</v>
       </c>
       <c r="U332" s="11" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="V332" s="11" t="s">
         <v>3492</v>
@@ -34757,7 +34758,7 @@
       </c>
       <c r="X332" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="333" spans="1:24" x14ac:dyDescent="0.3">
@@ -34809,7 +34810,7 @@
       </c>
       <c r="X333" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="334" spans="1:24" x14ac:dyDescent="0.3">
@@ -34870,7 +34871,7 @@
       </c>
       <c r="X334" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="335" spans="1:24" x14ac:dyDescent="0.3">
@@ -34917,7 +34918,7 @@
       </c>
       <c r="X335" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-3138</v>
+        <v>-3289</v>
       </c>
     </row>
     <row r="336" spans="1:24" x14ac:dyDescent="0.3">
@@ -34966,7 +34967,7 @@
       </c>
       <c r="X336" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="337" spans="1:24" x14ac:dyDescent="0.3">
@@ -35015,7 +35016,7 @@
       </c>
       <c r="X337" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="338" spans="1:24" x14ac:dyDescent="0.3">
@@ -35053,7 +35054,7 @@
         <v>1305</v>
       </c>
       <c r="U338" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V338" t="s">
         <v>3494</v>
@@ -35064,7 +35065,7 @@
       </c>
       <c r="X338" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="339" spans="1:24" x14ac:dyDescent="0.3">
@@ -35116,7 +35117,7 @@
       </c>
       <c r="X339" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="340" spans="1:24" x14ac:dyDescent="0.3">
@@ -35154,7 +35155,7 @@
         <v>1320</v>
       </c>
       <c r="U340" s="11" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="V340" s="11" t="s">
         <v>2648</v>
@@ -35165,7 +35166,7 @@
       </c>
       <c r="X340" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="341" spans="1:24" x14ac:dyDescent="0.3">
@@ -35214,7 +35215,7 @@
       </c>
       <c r="X341" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="342" spans="1:24" x14ac:dyDescent="0.3">
@@ -35266,7 +35267,7 @@
       </c>
       <c r="X342" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="343" spans="1:24" x14ac:dyDescent="0.3">
@@ -35315,7 +35316,7 @@
       </c>
       <c r="X343" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="344" spans="1:24" x14ac:dyDescent="0.3">
@@ -35353,7 +35354,7 @@
         <v>1349</v>
       </c>
       <c r="U344" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="V344" t="s">
         <v>3495</v>
@@ -35364,7 +35365,7 @@
       </c>
       <c r="X344" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="345" spans="1:24" x14ac:dyDescent="0.3">
@@ -35405,7 +35406,7 @@
         <v>1140</v>
       </c>
       <c r="U345" s="11" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="V345" s="11" t="s">
         <v>3405</v>
@@ -35416,7 +35417,7 @@
       </c>
       <c r="X345" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-244</v>
+        <v>-395</v>
       </c>
     </row>
     <row r="346" spans="1:24" x14ac:dyDescent="0.3">
@@ -35462,7 +35463,7 @@
       </c>
       <c r="X346" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="347" spans="1:24" x14ac:dyDescent="0.3">
@@ -35500,7 +35501,7 @@
         <v>1386</v>
       </c>
       <c r="U347" s="11" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="V347" s="11" t="s">
         <v>2715</v>
@@ -35511,7 +35512,7 @@
       </c>
       <c r="X347" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="348" spans="1:24" x14ac:dyDescent="0.3">
@@ -35563,7 +35564,7 @@
       </c>
       <c r="X348" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="349" spans="1:24" x14ac:dyDescent="0.3">
@@ -35615,7 +35616,7 @@
       </c>
       <c r="X349" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="350" spans="1:24" x14ac:dyDescent="0.3">
@@ -35653,7 +35654,7 @@
         <v>1347</v>
       </c>
       <c r="U350" s="11" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="V350" s="11" t="s">
         <v>3496</v>
@@ -35664,7 +35665,7 @@
       </c>
       <c r="X350" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="351" spans="1:24" x14ac:dyDescent="0.3">
@@ -35702,7 +35703,7 @@
         <v>1388</v>
       </c>
       <c r="U351" s="11" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="V351" s="11" t="s">
         <v>2181</v>
@@ -35713,7 +35714,7 @@
       </c>
       <c r="X351" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="352" spans="1:24" x14ac:dyDescent="0.3">
@@ -35762,7 +35763,7 @@
       </c>
       <c r="X352" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="353" spans="1:24" x14ac:dyDescent="0.3">
@@ -35814,7 +35815,7 @@
       </c>
       <c r="X353" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="354" spans="1:24" x14ac:dyDescent="0.3">
@@ -35860,7 +35861,7 @@
       </c>
       <c r="X354" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="355" spans="1:24" x14ac:dyDescent="0.3">
@@ -35909,7 +35910,7 @@
       </c>
       <c r="X355" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-794</v>
+        <v>-945</v>
       </c>
     </row>
     <row r="356" spans="1:24" x14ac:dyDescent="0.3">
@@ -35958,7 +35959,7 @@
       </c>
       <c r="X356" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="357" spans="1:24" x14ac:dyDescent="0.3">
@@ -36010,7 +36011,7 @@
       </c>
       <c r="X357" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="358" spans="1:24" x14ac:dyDescent="0.3">
@@ -36062,7 +36063,7 @@
       </c>
       <c r="X358" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="359" spans="1:24" x14ac:dyDescent="0.3">
@@ -36100,7 +36101,7 @@
         <v>1349</v>
       </c>
       <c r="U359" s="11" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="V359" s="11" t="s">
         <v>2759</v>
@@ -36111,7 +36112,7 @@
       </c>
       <c r="X359" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="360" spans="1:24" x14ac:dyDescent="0.3">
@@ -36160,7 +36161,7 @@
       </c>
       <c r="X360" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="361" spans="1:24" x14ac:dyDescent="0.3">
@@ -36212,7 +36213,7 @@
       </c>
       <c r="X361" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="362" spans="1:24" x14ac:dyDescent="0.3">
@@ -36261,7 +36262,7 @@
       </c>
       <c r="X362" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="363" spans="1:24" x14ac:dyDescent="0.3">
@@ -36299,7 +36300,7 @@
         <v>1394</v>
       </c>
       <c r="U363" s="11" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="V363" s="11" t="s">
         <v>3499</v>
@@ -36310,7 +36311,7 @@
       </c>
       <c r="X363" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="364" spans="1:24" x14ac:dyDescent="0.3">
@@ -36362,7 +36363,7 @@
       </c>
       <c r="X364" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="365" spans="1:24" x14ac:dyDescent="0.3">
@@ -36414,7 +36415,7 @@
       </c>
       <c r="X365" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="366" spans="1:24" x14ac:dyDescent="0.3">
@@ -36452,7 +36453,7 @@
         <v>1397</v>
       </c>
       <c r="U366" s="11" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="V366" s="11" t="s">
         <v>2756</v>
@@ -36463,7 +36464,7 @@
       </c>
       <c r="X366" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="367" spans="1:24" x14ac:dyDescent="0.3">
@@ -36512,7 +36513,7 @@
       </c>
       <c r="X367" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="368" spans="1:24" x14ac:dyDescent="0.3">
@@ -36564,7 +36565,7 @@
       </c>
       <c r="X368" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="369" spans="1:24" x14ac:dyDescent="0.3">
@@ -36608,7 +36609,7 @@
         <v>1318</v>
       </c>
       <c r="U369" s="11" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="V369" s="11" t="s">
         <v>3020</v>
@@ -36619,7 +36620,7 @@
       </c>
       <c r="X369" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="370" spans="1:24" x14ac:dyDescent="0.3">
@@ -36671,7 +36672,7 @@
       </c>
       <c r="X370" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="371" spans="1:24" x14ac:dyDescent="0.3">
@@ -36720,7 +36721,7 @@
       </c>
       <c r="X371" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="372" spans="1:24" x14ac:dyDescent="0.3">
@@ -36776,7 +36777,7 @@
       </c>
       <c r="X372" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-4234</v>
+        <v>-4385</v>
       </c>
     </row>
     <row r="373" spans="1:24" x14ac:dyDescent="0.3">
@@ -36828,7 +36829,7 @@
       </c>
       <c r="X373" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="374" spans="1:24" x14ac:dyDescent="0.3">
@@ -36869,7 +36870,7 @@
         <v>1368</v>
       </c>
       <c r="U374" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V374" s="11" t="s">
         <v>3502</v>
@@ -36880,7 +36881,7 @@
       </c>
       <c r="X374" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="375" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -36927,7 +36928,7 @@
         <v>1272</v>
       </c>
       <c r="U375" s="11" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="V375" s="11" t="s">
         <v>3503</v>
@@ -36938,7 +36939,7 @@
       </c>
       <c r="X375" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="376" spans="1:24" x14ac:dyDescent="0.3">
@@ -36987,7 +36988,7 @@
       </c>
       <c r="X376" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="377" spans="1:24" x14ac:dyDescent="0.3">
@@ -37036,7 +37037,7 @@
       </c>
       <c r="X377" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>241</v>
+        <v>90</v>
       </c>
     </row>
     <row r="378" spans="1:24" x14ac:dyDescent="0.3">
@@ -37077,7 +37078,7 @@
         <v>1215</v>
       </c>
       <c r="U378" s="11" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="V378" s="11" t="s">
         <v>3260</v>
@@ -37088,7 +37089,7 @@
       </c>
       <c r="X378" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="379" spans="1:24" x14ac:dyDescent="0.3">
@@ -37137,7 +37138,7 @@
       </c>
       <c r="X379" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="380" spans="1:24" x14ac:dyDescent="0.3">
@@ -37175,7 +37176,7 @@
         <v>1403</v>
       </c>
       <c r="U380" s="11" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="V380" s="11" t="s">
         <v>1674</v>
@@ -37186,7 +37187,7 @@
       </c>
       <c r="X380" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="381" spans="1:24" x14ac:dyDescent="0.3">
@@ -37235,7 +37236,7 @@
       </c>
       <c r="X381" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="382" spans="1:24" x14ac:dyDescent="0.3">
@@ -37284,7 +37285,7 @@
       </c>
       <c r="X382" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="383" spans="1:24" x14ac:dyDescent="0.3">
@@ -37336,7 +37337,7 @@
       </c>
       <c r="X383" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="384" spans="1:24" x14ac:dyDescent="0.3">
@@ -37385,7 +37386,7 @@
       </c>
       <c r="X384" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-428</v>
+        <v>-579</v>
       </c>
     </row>
     <row r="385" spans="1:24" x14ac:dyDescent="0.3">
@@ -37423,7 +37424,7 @@
         <v>1368</v>
       </c>
       <c r="U385" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V385" s="11" t="s">
         <v>3506</v>
@@ -37434,7 +37435,7 @@
       </c>
       <c r="X385" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="386" spans="1:24" x14ac:dyDescent="0.3">
@@ -37483,7 +37484,7 @@
       </c>
       <c r="X386" s="11">
         <f t="shared" ca="1" si="5"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="387" spans="1:24" x14ac:dyDescent="0.3">
@@ -37497,7 +37498,7 @@
         <v>111</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="E387" s="11" t="s">
         <v>2827</v>
@@ -37521,7 +37522,7 @@
         <v>1264</v>
       </c>
       <c r="U387" s="11" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="V387" s="11" t="s">
         <v>3507</v>
@@ -37532,7 +37533,7 @@
       </c>
       <c r="X387" s="11">
         <f t="shared" ref="X387:X450" ca="1" si="6">W387-TODAY()</f>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="388" spans="1:24" x14ac:dyDescent="0.3">
@@ -37570,7 +37571,7 @@
         <v>1407</v>
       </c>
       <c r="U388" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V388" s="11" t="s">
         <v>2389</v>
@@ -37581,7 +37582,7 @@
       </c>
       <c r="X388" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="389" spans="1:24" x14ac:dyDescent="0.3">
@@ -37627,7 +37628,7 @@
       </c>
       <c r="X389" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="390" spans="1:24" x14ac:dyDescent="0.3">
@@ -37673,7 +37674,7 @@
       </c>
       <c r="X390" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="391" spans="1:24" x14ac:dyDescent="0.3">
@@ -37725,7 +37726,7 @@
       </c>
       <c r="X391" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="392" spans="1:24" x14ac:dyDescent="0.3">
@@ -37774,7 +37775,7 @@
       </c>
       <c r="X392" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="393" spans="1:24" x14ac:dyDescent="0.3">
@@ -37823,7 +37824,7 @@
       </c>
       <c r="X393" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="394" spans="1:24" x14ac:dyDescent="0.3">
@@ -37884,7 +37885,7 @@
       </c>
       <c r="X394" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="395" spans="1:24" x14ac:dyDescent="0.3">
@@ -37936,7 +37937,7 @@
       </c>
       <c r="X395" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="396" spans="1:24" x14ac:dyDescent="0.3">
@@ -37977,7 +37978,7 @@
         <v>1201</v>
       </c>
       <c r="U396" s="11" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="V396" s="11" t="s">
         <v>2917</v>
@@ -37988,7 +37989,7 @@
       </c>
       <c r="X396" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="397" spans="1:24" x14ac:dyDescent="0.3">
@@ -38034,7 +38035,7 @@
       </c>
       <c r="X397" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="398" spans="1:24" x14ac:dyDescent="0.3">
@@ -38072,7 +38073,7 @@
         <v>1407</v>
       </c>
       <c r="U398" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V398" s="11" t="s">
         <v>3510</v>
@@ -38083,7 +38084,7 @@
       </c>
       <c r="X398" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="399" spans="1:24" x14ac:dyDescent="0.3">
@@ -38121,7 +38122,7 @@
         <v>1272</v>
       </c>
       <c r="U399" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V399" s="11" t="s">
         <v>2396</v>
@@ -38132,7 +38133,7 @@
       </c>
       <c r="X399" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="400" spans="1:24" x14ac:dyDescent="0.3">
@@ -38170,7 +38171,7 @@
         <v>1411</v>
       </c>
       <c r="U400" s="11" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="V400" s="11" t="s">
         <v>2231</v>
@@ -38181,7 +38182,7 @@
       </c>
       <c r="X400" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="401" spans="1:24" x14ac:dyDescent="0.3">
@@ -38230,7 +38231,7 @@
       </c>
       <c r="X401" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="402" spans="1:24" x14ac:dyDescent="0.3">
@@ -38282,7 +38283,7 @@
       </c>
       <c r="X402" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="403" spans="1:24" x14ac:dyDescent="0.3">
@@ -38320,7 +38321,7 @@
         <v>1368</v>
       </c>
       <c r="U403" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V403" s="11" t="s">
         <v>1908</v>
@@ -38331,7 +38332,7 @@
       </c>
       <c r="X403" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="404" spans="1:24" x14ac:dyDescent="0.3">
@@ -38369,7 +38370,7 @@
         <v>1365</v>
       </c>
       <c r="U404" s="11" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="V404" s="11" t="s">
         <v>2533</v>
@@ -38380,7 +38381,7 @@
       </c>
       <c r="X404" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="405" spans="1:24" x14ac:dyDescent="0.3">
@@ -38435,7 +38436,7 @@
       </c>
       <c r="X405" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="406" spans="1:24" x14ac:dyDescent="0.3">
@@ -38473,7 +38474,7 @@
         <v>1368</v>
       </c>
       <c r="U406" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V406" s="11" t="s">
         <v>3506</v>
@@ -38484,7 +38485,7 @@
       </c>
       <c r="X406" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="407" spans="1:24" x14ac:dyDescent="0.3">
@@ -38539,7 +38540,7 @@
       </c>
       <c r="X407" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="408" spans="1:24" x14ac:dyDescent="0.3">
@@ -38577,7 +38578,7 @@
         <v>1415</v>
       </c>
       <c r="U408" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V408" s="11" t="s">
         <v>3511</v>
@@ -38588,7 +38589,7 @@
       </c>
       <c r="X408" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="409" spans="1:24" x14ac:dyDescent="0.3">
@@ -38640,7 +38641,7 @@
       </c>
       <c r="X409" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="410" spans="1:24" x14ac:dyDescent="0.3">
@@ -38692,7 +38693,7 @@
       </c>
       <c r="X410" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="411" spans="1:24" x14ac:dyDescent="0.3">
@@ -38741,7 +38742,7 @@
       </c>
       <c r="X411" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="412" spans="1:24" x14ac:dyDescent="0.3">
@@ -38787,7 +38788,7 @@
       </c>
       <c r="X412" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="413" spans="1:24" x14ac:dyDescent="0.3">
@@ -38836,7 +38837,7 @@
       </c>
       <c r="X413" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="414" spans="1:24" x14ac:dyDescent="0.3">
@@ -38888,7 +38889,7 @@
       </c>
       <c r="X414" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>180</v>
+        <v>29</v>
       </c>
     </row>
     <row r="415" spans="1:24" x14ac:dyDescent="0.3">
@@ -38937,7 +38938,7 @@
       </c>
       <c r="X415" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="416" spans="1:24" x14ac:dyDescent="0.3">
@@ -38986,7 +38987,7 @@
       </c>
       <c r="X416" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="417" spans="1:24" x14ac:dyDescent="0.3">
@@ -39035,7 +39036,7 @@
       </c>
       <c r="X417" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="418" spans="1:24" x14ac:dyDescent="0.3">
@@ -39084,7 +39085,7 @@
       </c>
       <c r="X418" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="419" spans="1:24" x14ac:dyDescent="0.3">
@@ -39122,7 +39123,7 @@
         <v>1272</v>
       </c>
       <c r="U419" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V419" s="11" t="s">
         <v>2460</v>
@@ -39133,7 +39134,7 @@
       </c>
       <c r="X419" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="420" spans="1:24" x14ac:dyDescent="0.3">
@@ -39171,7 +39172,7 @@
         <v>1403</v>
       </c>
       <c r="U420" s="11" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="V420" s="11" t="s">
         <v>3364</v>
@@ -39182,7 +39183,7 @@
       </c>
       <c r="X420" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="421" spans="1:24" x14ac:dyDescent="0.3">
@@ -39220,7 +39221,7 @@
         <v>1272</v>
       </c>
       <c r="U421" s="11" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="V421" s="11" t="s">
         <v>2278</v>
@@ -39231,7 +39232,7 @@
       </c>
       <c r="X421" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="422" spans="1:24" x14ac:dyDescent="0.3">
@@ -39269,7 +39270,7 @@
         <v>1419</v>
       </c>
       <c r="U422" s="11" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="V422" s="11" t="s">
         <v>2710</v>
@@ -39280,7 +39281,7 @@
       </c>
       <c r="X422" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="423" spans="1:24" x14ac:dyDescent="0.3">
@@ -39318,7 +39319,7 @@
         <v>1368</v>
       </c>
       <c r="U423" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V423" s="11" t="s">
         <v>2186</v>
@@ -39329,7 +39330,7 @@
       </c>
       <c r="X423" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="424" spans="1:24" x14ac:dyDescent="0.3">
@@ -39367,7 +39368,7 @@
         <v>1305</v>
       </c>
       <c r="U424" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V424" s="11" t="s">
         <v>2647</v>
@@ -39378,7 +39379,7 @@
       </c>
       <c r="X424" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="425" spans="1:24" x14ac:dyDescent="0.3">
@@ -39416,7 +39417,7 @@
         <v>1272</v>
       </c>
       <c r="U425" s="11" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="V425" s="11" t="s">
         <v>2455</v>
@@ -39427,7 +39428,7 @@
       </c>
       <c r="X425" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="426" spans="1:24" x14ac:dyDescent="0.3">
@@ -39465,7 +39466,7 @@
         <v>1422</v>
       </c>
       <c r="U426" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V426" s="11" t="s">
         <v>2174</v>
@@ -39476,7 +39477,7 @@
       </c>
       <c r="X426" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="427" spans="1:24" x14ac:dyDescent="0.3">
@@ -39525,7 +39526,7 @@
       </c>
       <c r="X427" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="428" spans="1:24" x14ac:dyDescent="0.3">
@@ -39574,7 +39575,7 @@
       </c>
       <c r="X428" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="429" spans="1:24" x14ac:dyDescent="0.3">
@@ -39612,7 +39613,7 @@
         <v>1272</v>
       </c>
       <c r="U429" s="11" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="V429" s="11" t="s">
         <v>3516</v>
@@ -39623,7 +39624,7 @@
       </c>
       <c r="X429" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="430" spans="1:24" x14ac:dyDescent="0.3">
@@ -39661,7 +39662,7 @@
         <v>1272</v>
       </c>
       <c r="U430" s="11" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="V430" s="11" t="s">
         <v>2449</v>
@@ -39672,7 +39673,7 @@
       </c>
       <c r="X430" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="431" spans="1:24" x14ac:dyDescent="0.3">
@@ -39710,7 +39711,7 @@
         <v>1424</v>
       </c>
       <c r="U431" s="11" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="V431" s="11" t="s">
         <v>2525</v>
@@ -39721,7 +39722,7 @@
       </c>
       <c r="X431" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="432" spans="1:24" x14ac:dyDescent="0.3">
@@ -39773,7 +39774,7 @@
       </c>
       <c r="X432" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="433" spans="1:24" x14ac:dyDescent="0.3">
@@ -39811,10 +39812,10 @@
         <v>1336</v>
       </c>
       <c r="U433" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="V433" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="W433" s="54">
         <f>INDEX([1]ACOMPANHAMENTO!H:H,MATCH(A433,[1]ACOMPANHAMENTO!A:A,0))</f>
@@ -39822,7 +39823,7 @@
       </c>
       <c r="X433" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="434" spans="1:24" x14ac:dyDescent="0.3">
@@ -39871,7 +39872,7 @@
       </c>
       <c r="X434" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="435" spans="1:24" x14ac:dyDescent="0.3">
@@ -39920,7 +39921,7 @@
       </c>
       <c r="X435" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="436" spans="1:24" x14ac:dyDescent="0.3">
@@ -39958,7 +39959,7 @@
         <v>1407</v>
       </c>
       <c r="U436" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V436" s="11" t="s">
         <v>3518</v>
@@ -39969,7 +39970,7 @@
       </c>
       <c r="X436" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="437" spans="1:24" x14ac:dyDescent="0.3">
@@ -40007,7 +40008,7 @@
         <v>1411</v>
       </c>
       <c r="U437" s="11" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="V437" s="11" t="s">
         <v>3519</v>
@@ -40018,7 +40019,7 @@
       </c>
       <c r="X437" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="438" spans="1:24" x14ac:dyDescent="0.3">
@@ -40056,7 +40057,7 @@
         <v>1272</v>
       </c>
       <c r="U438" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V438" s="11" t="s">
         <v>2336</v>
@@ -40067,7 +40068,7 @@
       </c>
       <c r="X438" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="439" spans="1:24" x14ac:dyDescent="0.3">
@@ -40105,7 +40106,7 @@
         <v>1424</v>
       </c>
       <c r="U439" s="11" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="V439" s="11" t="s">
         <v>2348</v>
@@ -40116,7 +40117,7 @@
       </c>
       <c r="X439" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="440" spans="1:24" x14ac:dyDescent="0.3">
@@ -40154,7 +40155,7 @@
         <v>1388</v>
       </c>
       <c r="U440" s="11" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="V440" s="11" t="s">
         <v>2383</v>
@@ -40165,7 +40166,7 @@
       </c>
       <c r="X440" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="441" spans="1:24" x14ac:dyDescent="0.3">
@@ -40217,7 +40218,7 @@
       </c>
       <c r="X441" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="442" spans="1:24" x14ac:dyDescent="0.3">
@@ -40255,7 +40256,7 @@
         <v>1305</v>
       </c>
       <c r="U442" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V442" s="11" t="s">
         <v>2673</v>
@@ -40266,7 +40267,7 @@
       </c>
       <c r="X442" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="443" spans="1:24" x14ac:dyDescent="0.3">
@@ -40304,7 +40305,7 @@
         <v>1425</v>
       </c>
       <c r="U443" s="11" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="V443" s="11" t="s">
         <v>2557</v>
@@ -40315,7 +40316,7 @@
       </c>
       <c r="X443" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="444" spans="1:24" x14ac:dyDescent="0.3">
@@ -40364,7 +40365,7 @@
       </c>
       <c r="X444" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="445" spans="1:24" x14ac:dyDescent="0.3">
@@ -40402,7 +40403,7 @@
         <v>1394</v>
       </c>
       <c r="U445" s="11" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="V445" s="11" t="s">
         <v>2274</v>
@@ -40413,7 +40414,7 @@
       </c>
       <c r="X445" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="446" spans="1:24" x14ac:dyDescent="0.3">
@@ -40462,7 +40463,7 @@
       </c>
       <c r="X446" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="447" spans="1:24" x14ac:dyDescent="0.3">
@@ -40500,7 +40501,7 @@
         <v>1370</v>
       </c>
       <c r="U447" s="11" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="V447" s="11" t="s">
         <v>3484</v>
@@ -40511,7 +40512,7 @@
       </c>
       <c r="X447" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="448" spans="1:24" x14ac:dyDescent="0.3">
@@ -40560,7 +40561,7 @@
       </c>
       <c r="X448" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="449" spans="1:24" x14ac:dyDescent="0.3">
@@ -40609,7 +40610,7 @@
       </c>
       <c r="X449" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="450" spans="1:24" x14ac:dyDescent="0.3">
@@ -40647,7 +40648,7 @@
         <v>1272</v>
       </c>
       <c r="U450" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V450" s="11" t="s">
         <v>2159</v>
@@ -40658,7 +40659,7 @@
       </c>
       <c r="X450" s="11">
         <f t="shared" ca="1" si="6"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="451" spans="1:24" x14ac:dyDescent="0.3">
@@ -40699,7 +40700,7 @@
         <v>1151</v>
       </c>
       <c r="U451" s="11" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="V451" s="11" t="s">
         <v>3520</v>
@@ -40710,7 +40711,7 @@
       </c>
       <c r="X451" s="11">
         <f t="shared" ref="X451:X514" ca="1" si="7">W451-TODAY()</f>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="452" spans="1:24" x14ac:dyDescent="0.3">
@@ -40748,7 +40749,7 @@
         <v>1305</v>
       </c>
       <c r="U452" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V452" s="11" t="s">
         <v>3521</v>
@@ -40759,7 +40760,7 @@
       </c>
       <c r="X452" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="453" spans="1:24" x14ac:dyDescent="0.3">
@@ -40808,7 +40809,7 @@
       </c>
       <c r="X453" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="454" spans="1:24" x14ac:dyDescent="0.3">
@@ -40860,7 +40861,7 @@
       </c>
       <c r="X454" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="455" spans="1:24" x14ac:dyDescent="0.3">
@@ -40898,7 +40899,7 @@
         <v>1428</v>
       </c>
       <c r="U455" s="11" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="V455" s="11" t="s">
         <v>2182</v>
@@ -40909,7 +40910,7 @@
       </c>
       <c r="X455" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="456" spans="1:24" x14ac:dyDescent="0.3">
@@ -40947,7 +40948,7 @@
         <v>1394</v>
       </c>
       <c r="U456" s="11" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="V456" s="11" t="s">
         <v>2482</v>
@@ -40958,7 +40959,7 @@
       </c>
       <c r="X456" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="457" spans="1:24" x14ac:dyDescent="0.3">
@@ -41010,7 +41011,7 @@
       </c>
       <c r="X457" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="458" spans="1:24" x14ac:dyDescent="0.3">
@@ -41048,7 +41049,7 @@
         <v>1415</v>
       </c>
       <c r="U458" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V458" s="11" t="s">
         <v>2292</v>
@@ -41059,7 +41060,7 @@
       </c>
       <c r="X458" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="459" spans="1:24" x14ac:dyDescent="0.3">
@@ -41108,7 +41109,7 @@
       </c>
       <c r="X459" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="460" spans="1:24" x14ac:dyDescent="0.3">
@@ -41157,7 +41158,7 @@
       </c>
       <c r="X460" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="461" spans="1:24" x14ac:dyDescent="0.3">
@@ -41206,7 +41207,7 @@
       </c>
       <c r="X461" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="462" spans="1:24" x14ac:dyDescent="0.3">
@@ -41244,7 +41245,7 @@
         <v>1428</v>
       </c>
       <c r="U462" s="11" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="V462" s="11" t="s">
         <v>2399</v>
@@ -41255,7 +41256,7 @@
       </c>
       <c r="X462" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="463" spans="1:24" x14ac:dyDescent="0.3">
@@ -41301,7 +41302,7 @@
       </c>
       <c r="X463" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="464" spans="1:24" x14ac:dyDescent="0.3">
@@ -41339,7 +41340,7 @@
         <v>1430</v>
       </c>
       <c r="U464" s="11" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="V464" s="11" t="s">
         <v>3524</v>
@@ -41350,7 +41351,7 @@
       </c>
       <c r="X464" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>241</v>
+        <v>90</v>
       </c>
     </row>
     <row r="465" spans="1:24" x14ac:dyDescent="0.3">
@@ -41388,7 +41389,7 @@
         <v>1272</v>
       </c>
       <c r="U465" s="11" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="V465" s="11" t="s">
         <v>3525</v>
@@ -41399,7 +41400,7 @@
       </c>
       <c r="X465" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="466" spans="1:24" x14ac:dyDescent="0.3">
@@ -41437,7 +41438,7 @@
         <v>1422</v>
       </c>
       <c r="U466" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V466" s="11" t="s">
         <v>3526</v>
@@ -41448,7 +41449,7 @@
       </c>
       <c r="X466" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="467" spans="1:24" x14ac:dyDescent="0.3">
@@ -41497,7 +41498,7 @@
       </c>
       <c r="X467" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="468" spans="1:24" x14ac:dyDescent="0.3">
@@ -41535,7 +41536,7 @@
         <v>1264</v>
       </c>
       <c r="U468" s="11" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="V468" s="11" t="s">
         <v>2902</v>
@@ -41546,7 +41547,7 @@
       </c>
       <c r="X468" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="469" spans="1:24" x14ac:dyDescent="0.3">
@@ -41584,7 +41585,7 @@
         <v>1365</v>
       </c>
       <c r="U469" s="11" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="V469" s="11" t="s">
         <v>2796</v>
@@ -41595,7 +41596,7 @@
       </c>
       <c r="X469" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="470" spans="1:24" x14ac:dyDescent="0.3">
@@ -41633,7 +41634,7 @@
         <v>1407</v>
       </c>
       <c r="U470" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V470" s="11" t="s">
         <v>3527</v>
@@ -41644,7 +41645,7 @@
       </c>
       <c r="X470" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="471" spans="1:24" x14ac:dyDescent="0.3">
@@ -41682,7 +41683,7 @@
         <v>1422</v>
       </c>
       <c r="U471" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V471" s="11" t="s">
         <v>2165</v>
@@ -41693,7 +41694,7 @@
       </c>
       <c r="X471" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="472" spans="1:24" x14ac:dyDescent="0.3">
@@ -41742,7 +41743,7 @@
       </c>
       <c r="X472" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="473" spans="1:24" x14ac:dyDescent="0.3">
@@ -41791,7 +41792,7 @@
       </c>
       <c r="X473" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="474" spans="1:24" x14ac:dyDescent="0.3">
@@ -41829,7 +41830,7 @@
         <v>1368</v>
       </c>
       <c r="U474" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V474" s="11" t="s">
         <v>2209</v>
@@ -41840,7 +41841,7 @@
       </c>
       <c r="X474" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="475" spans="1:24" x14ac:dyDescent="0.3">
@@ -41892,7 +41893,7 @@
       </c>
       <c r="X475" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="476" spans="1:24" x14ac:dyDescent="0.3">
@@ -41944,7 +41945,7 @@
       </c>
       <c r="X476" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="477" spans="1:24" x14ac:dyDescent="0.3">
@@ -41982,7 +41983,7 @@
         <v>1401</v>
       </c>
       <c r="U477" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V477" s="11" t="s">
         <v>2404</v>
@@ -41993,7 +41994,7 @@
       </c>
       <c r="X477" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>241</v>
+        <v>90</v>
       </c>
     </row>
     <row r="478" spans="1:24" x14ac:dyDescent="0.3">
@@ -42031,7 +42032,7 @@
         <v>1424</v>
       </c>
       <c r="U478" s="11" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="V478" s="11" t="s">
         <v>3529</v>
@@ -42042,7 +42043,7 @@
       </c>
       <c r="X478" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="479" spans="1:24" x14ac:dyDescent="0.3">
@@ -42080,7 +42081,7 @@
         <v>1411</v>
       </c>
       <c r="U479" s="11" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="V479" s="11" t="s">
         <v>2519</v>
@@ -42091,7 +42092,7 @@
       </c>
       <c r="X479" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="480" spans="1:24" x14ac:dyDescent="0.3">
@@ -42129,7 +42130,7 @@
         <v>1415</v>
       </c>
       <c r="U480" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V480" s="11" t="s">
         <v>3530</v>
@@ -42140,7 +42141,7 @@
       </c>
       <c r="X480" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="481" spans="1:24" x14ac:dyDescent="0.3">
@@ -42192,7 +42193,7 @@
       </c>
       <c r="X481" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="482" spans="1:24" x14ac:dyDescent="0.3">
@@ -42241,7 +42242,7 @@
       </c>
       <c r="X482" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="483" spans="1:24" x14ac:dyDescent="0.3">
@@ -42279,7 +42280,7 @@
         <v>1424</v>
       </c>
       <c r="U483" s="11" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="V483" s="11" t="s">
         <v>2401</v>
@@ -42290,7 +42291,7 @@
       </c>
       <c r="X483" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="484" spans="1:24" x14ac:dyDescent="0.3">
@@ -42328,7 +42329,7 @@
         <v>1434</v>
       </c>
       <c r="U484" s="11" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="V484" s="11" t="s">
         <v>3531</v>
@@ -42339,7 +42340,7 @@
       </c>
       <c r="X484" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="485" spans="1:24" x14ac:dyDescent="0.3">
@@ -42377,7 +42378,7 @@
         <v>1272</v>
       </c>
       <c r="U485" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V485" s="11" t="s">
         <v>3532</v>
@@ -42388,7 +42389,7 @@
       </c>
       <c r="X485" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="486" spans="1:24" x14ac:dyDescent="0.3">
@@ -42426,7 +42427,7 @@
         <v>1406</v>
       </c>
       <c r="U486" s="11" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="V486" s="11" t="s">
         <v>2376</v>
@@ -42437,7 +42438,7 @@
       </c>
       <c r="X486" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="487" spans="1:24" x14ac:dyDescent="0.3">
@@ -42489,7 +42490,7 @@
       </c>
       <c r="X487" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-185</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="488" spans="1:24" x14ac:dyDescent="0.3">
@@ -42527,7 +42528,7 @@
         <v>1422</v>
       </c>
       <c r="U488" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V488" s="11" t="s">
         <v>3533</v>
@@ -42538,7 +42539,7 @@
       </c>
       <c r="X488" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="489" spans="1:24" x14ac:dyDescent="0.3">
@@ -42590,7 +42591,7 @@
       </c>
       <c r="X489" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="490" spans="1:24" x14ac:dyDescent="0.3">
@@ -42639,7 +42640,7 @@
       </c>
       <c r="X490" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="491" spans="1:24" x14ac:dyDescent="0.3">
@@ -42680,7 +42681,7 @@
         <v>1436</v>
       </c>
       <c r="U491" s="11" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="V491" s="11" t="s">
         <v>1900</v>
@@ -42691,7 +42692,7 @@
       </c>
       <c r="X491" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="492" spans="1:24" x14ac:dyDescent="0.3">
@@ -42729,7 +42730,7 @@
         <v>1368</v>
       </c>
       <c r="U492" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V492" s="11" t="s">
         <v>2462</v>
@@ -42740,7 +42741,7 @@
       </c>
       <c r="X492" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="493" spans="1:24" x14ac:dyDescent="0.3">
@@ -42792,7 +42793,7 @@
       </c>
       <c r="X493" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-2</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="494" spans="1:24" x14ac:dyDescent="0.3">
@@ -42841,7 +42842,7 @@
       </c>
       <c r="X494" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="495" spans="1:24" x14ac:dyDescent="0.3">
@@ -42879,7 +42880,7 @@
         <v>1439</v>
       </c>
       <c r="U495" s="11" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="V495" s="11" t="s">
         <v>3534</v>
@@ -42890,7 +42891,7 @@
       </c>
       <c r="X495" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="496" spans="1:24" x14ac:dyDescent="0.3">
@@ -42928,7 +42929,7 @@
         <v>1424</v>
       </c>
       <c r="U496" s="11" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="V496" s="11" t="s">
         <v>2299</v>
@@ -42939,7 +42940,7 @@
       </c>
       <c r="X496" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="497" spans="1:24" x14ac:dyDescent="0.3">
@@ -42977,7 +42978,7 @@
         <v>1305</v>
       </c>
       <c r="U497" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V497" s="11" t="s">
         <v>3535</v>
@@ -42988,7 +42989,7 @@
       </c>
       <c r="X497" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="498" spans="1:24" x14ac:dyDescent="0.3">
@@ -43026,7 +43027,7 @@
         <v>1347</v>
       </c>
       <c r="U498" s="11" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="V498" s="11" t="s">
         <v>2654</v>
@@ -43037,7 +43038,7 @@
       </c>
       <c r="X498" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="499" spans="1:24" x14ac:dyDescent="0.3">
@@ -43075,7 +43076,7 @@
         <v>1441</v>
       </c>
       <c r="U499" s="11" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="V499" s="11" t="s">
         <v>3536</v>
@@ -43086,7 +43087,7 @@
       </c>
       <c r="X499" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="500" spans="1:24" x14ac:dyDescent="0.3">
@@ -43127,7 +43128,7 @@
         <v>1442</v>
       </c>
       <c r="U500" s="11" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="V500" s="11" t="s">
         <v>1576</v>
@@ -43138,7 +43139,7 @@
       </c>
       <c r="X500" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="501" spans="1:24" x14ac:dyDescent="0.3">
@@ -43176,7 +43177,7 @@
         <v>1445</v>
       </c>
       <c r="U501" s="11" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="V501" s="11" t="s">
         <v>3537</v>
@@ -43187,7 +43188,7 @@
       </c>
       <c r="X501" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="502" spans="1:24" x14ac:dyDescent="0.3">
@@ -43236,7 +43237,7 @@
       </c>
       <c r="X502" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="503" spans="1:24" x14ac:dyDescent="0.3">
@@ -43274,7 +43275,7 @@
         <v>1272</v>
       </c>
       <c r="U503" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V503" s="11" t="s">
         <v>2351</v>
@@ -43285,7 +43286,7 @@
       </c>
       <c r="X503" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="504" spans="1:24" x14ac:dyDescent="0.3">
@@ -43323,7 +43324,7 @@
         <v>1407</v>
       </c>
       <c r="U504" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V504" s="11" t="s">
         <v>2342</v>
@@ -43334,7 +43335,7 @@
       </c>
       <c r="X504" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="505" spans="1:24" x14ac:dyDescent="0.3">
@@ -43372,7 +43373,7 @@
         <v>1272</v>
       </c>
       <c r="U505" s="11" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="V505" s="11" t="s">
         <v>2247</v>
@@ -43383,7 +43384,7 @@
       </c>
       <c r="X505" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="506" spans="1:24" x14ac:dyDescent="0.3">
@@ -43421,7 +43422,7 @@
         <v>1349</v>
       </c>
       <c r="U506" s="11" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="V506" s="11" t="s">
         <v>2738</v>
@@ -43432,7 +43433,7 @@
       </c>
       <c r="X506" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="507" spans="1:24" x14ac:dyDescent="0.3">
@@ -43470,7 +43471,7 @@
         <v>1448</v>
       </c>
       <c r="U507" s="11" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="V507" s="11" t="s">
         <v>1949</v>
@@ -43481,7 +43482,7 @@
       </c>
       <c r="X507" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="508" spans="1:24" x14ac:dyDescent="0.3">
@@ -43519,7 +43520,7 @@
         <v>1415</v>
       </c>
       <c r="U508" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V508" s="11" t="s">
         <v>3538</v>
@@ -43530,7 +43531,7 @@
       </c>
       <c r="X508" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="509" spans="1:24" x14ac:dyDescent="0.3">
@@ -43568,7 +43569,7 @@
         <v>1272</v>
       </c>
       <c r="U509" s="11" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="V509" s="11" t="s">
         <v>2813</v>
@@ -43579,7 +43580,7 @@
       </c>
       <c r="X509" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="510" spans="1:24" x14ac:dyDescent="0.3">
@@ -43628,7 +43629,7 @@
       </c>
       <c r="X510" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="511" spans="1:24" x14ac:dyDescent="0.3">
@@ -43677,7 +43678,7 @@
       </c>
       <c r="X511" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="512" spans="1:24" x14ac:dyDescent="0.3">
@@ -43715,7 +43716,7 @@
         <v>1449</v>
       </c>
       <c r="U512" s="11" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="V512" s="11" t="s">
         <v>3539</v>
@@ -43726,7 +43727,7 @@
       </c>
       <c r="X512" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="513" spans="1:24" x14ac:dyDescent="0.3">
@@ -43764,7 +43765,7 @@
         <v>1365</v>
       </c>
       <c r="U513" s="11" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="V513" s="11" t="s">
         <v>2677</v>
@@ -43775,7 +43776,7 @@
       </c>
       <c r="X513" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="514" spans="1:24" x14ac:dyDescent="0.3">
@@ -43824,7 +43825,7 @@
       </c>
       <c r="X514" s="11">
         <f t="shared" ca="1" si="7"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="515" spans="1:24" x14ac:dyDescent="0.3">
@@ -43862,7 +43863,7 @@
         <v>1403</v>
       </c>
       <c r="U515" s="11" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="V515" s="11" t="s">
         <v>3540</v>
@@ -43873,7 +43874,7 @@
       </c>
       <c r="X515" s="11">
         <f t="shared" ref="X515:X578" ca="1" si="8">W515-TODAY()</f>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="516" spans="1:24" x14ac:dyDescent="0.3">
@@ -43911,7 +43912,7 @@
         <v>1422</v>
       </c>
       <c r="U516" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V516" s="11" t="s">
         <v>3541</v>
@@ -43922,7 +43923,7 @@
       </c>
       <c r="X516" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="517" spans="1:24" x14ac:dyDescent="0.3">
@@ -43960,7 +43961,7 @@
         <v>1452</v>
       </c>
       <c r="U517" s="11" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="V517" s="11" t="s">
         <v>3542</v>
@@ -43971,7 +43972,7 @@
       </c>
       <c r="X517" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>394</v>
+        <v>243</v>
       </c>
     </row>
     <row r="518" spans="1:24" x14ac:dyDescent="0.3">
@@ -44009,7 +44010,7 @@
         <v>1430</v>
       </c>
       <c r="U518" s="11" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="V518" s="11" t="s">
         <v>2355</v>
@@ -44020,7 +44021,7 @@
       </c>
       <c r="X518" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>241</v>
+        <v>90</v>
       </c>
     </row>
     <row r="519" spans="1:24" x14ac:dyDescent="0.3">
@@ -44058,7 +44059,7 @@
         <v>1455</v>
       </c>
       <c r="U519" s="11" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="V519" s="11" t="s">
         <v>3394</v>
@@ -44069,7 +44070,7 @@
       </c>
       <c r="X519" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="520" spans="1:24" x14ac:dyDescent="0.3">
@@ -44107,7 +44108,7 @@
         <v>1457</v>
       </c>
       <c r="U520" s="11" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="V520" s="11" t="s">
         <v>3354</v>
@@ -44118,7 +44119,7 @@
       </c>
       <c r="X520" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="521" spans="1:24" x14ac:dyDescent="0.3">
@@ -44156,7 +44157,7 @@
         <v>1336</v>
       </c>
       <c r="U521" s="11" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="V521" s="11" t="s">
         <v>2680</v>
@@ -44167,7 +44168,7 @@
       </c>
       <c r="X521" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="522" spans="1:24" x14ac:dyDescent="0.3">
@@ -44216,7 +44217,7 @@
       </c>
       <c r="X522" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="523" spans="1:24" x14ac:dyDescent="0.3">
@@ -44254,7 +44255,7 @@
         <v>1407</v>
       </c>
       <c r="U523" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V523" s="11" t="s">
         <v>2524</v>
@@ -44265,7 +44266,7 @@
       </c>
       <c r="X523" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="524" spans="1:24" x14ac:dyDescent="0.3">
@@ -44314,7 +44315,7 @@
       </c>
       <c r="X524" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="525" spans="1:24" x14ac:dyDescent="0.3">
@@ -44363,7 +44364,7 @@
       </c>
       <c r="X525" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="526" spans="1:24" x14ac:dyDescent="0.3">
@@ -44412,7 +44413,7 @@
       </c>
       <c r="X526" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="527" spans="1:24" x14ac:dyDescent="0.3">
@@ -44450,7 +44451,7 @@
         <v>1458</v>
       </c>
       <c r="U527" s="11" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="V527" s="11" t="s">
         <v>3546</v>
@@ -44461,7 +44462,7 @@
       </c>
       <c r="X527" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>394</v>
+        <v>243</v>
       </c>
     </row>
     <row r="528" spans="1:24" x14ac:dyDescent="0.3">
@@ -44499,7 +44500,7 @@
         <v>1305</v>
       </c>
       <c r="U528" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V528" s="11" t="s">
         <v>3547</v>
@@ -44510,7 +44511,7 @@
       </c>
       <c r="X528" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="529" spans="1:24" x14ac:dyDescent="0.3">
@@ -44548,7 +44549,7 @@
         <v>1272</v>
       </c>
       <c r="U529" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V529" s="11" t="s">
         <v>2451</v>
@@ -44559,7 +44560,7 @@
       </c>
       <c r="X529" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="530" spans="1:24" x14ac:dyDescent="0.3">
@@ -44597,7 +44598,7 @@
         <v>1461</v>
       </c>
       <c r="U530" s="11" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="V530" s="11" t="s">
         <v>3548</v>
@@ -44608,7 +44609,7 @@
       </c>
       <c r="X530" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="531" spans="1:24" x14ac:dyDescent="0.3">
@@ -44657,7 +44658,7 @@
       </c>
       <c r="X531" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="532" spans="1:24" x14ac:dyDescent="0.3">
@@ -44695,7 +44696,7 @@
         <v>1422</v>
       </c>
       <c r="U532" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V532" s="11" t="s">
         <v>3549</v>
@@ -44706,7 +44707,7 @@
       </c>
       <c r="X532" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="533" spans="1:24" x14ac:dyDescent="0.3">
@@ -44744,7 +44745,7 @@
         <v>1415</v>
       </c>
       <c r="U533" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V533" s="11" t="s">
         <v>2515</v>
@@ -44755,7 +44756,7 @@
       </c>
       <c r="X533" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="534" spans="1:24" x14ac:dyDescent="0.3">
@@ -44793,7 +44794,7 @@
         <v>1422</v>
       </c>
       <c r="U534" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V534" s="11" t="s">
         <v>3550</v>
@@ -44804,7 +44805,7 @@
       </c>
       <c r="X534" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="535" spans="1:24" x14ac:dyDescent="0.3">
@@ -44853,7 +44854,7 @@
       </c>
       <c r="X535" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="536" spans="1:24" x14ac:dyDescent="0.3">
@@ -44891,7 +44892,7 @@
         <v>1272</v>
       </c>
       <c r="U536" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V536" s="11" t="s">
         <v>3552</v>
@@ -44902,7 +44903,7 @@
       </c>
       <c r="X536" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="537" spans="1:24" x14ac:dyDescent="0.3">
@@ -44951,7 +44952,7 @@
       </c>
       <c r="X537" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="538" spans="1:24" x14ac:dyDescent="0.3">
@@ -44989,7 +44990,7 @@
         <v>1434</v>
       </c>
       <c r="U538" s="11" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="V538" s="11" t="s">
         <v>1976</v>
@@ -45000,7 +45001,7 @@
       </c>
       <c r="X538" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="539" spans="1:24" x14ac:dyDescent="0.3">
@@ -45038,7 +45039,7 @@
         <v>1403</v>
       </c>
       <c r="U539" s="11" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="V539" s="11" t="s">
         <v>3553</v>
@@ -45049,7 +45050,7 @@
       </c>
       <c r="X539" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="540" spans="1:24" x14ac:dyDescent="0.3">
@@ -45101,7 +45102,7 @@
       </c>
       <c r="X540" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="541" spans="1:24" x14ac:dyDescent="0.3">
@@ -45150,7 +45151,7 @@
       </c>
       <c r="X541" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="542" spans="1:24" x14ac:dyDescent="0.3">
@@ -45188,7 +45189,7 @@
         <v>1368</v>
       </c>
       <c r="U542" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V542" s="11" t="s">
         <v>2333</v>
@@ -45199,7 +45200,7 @@
       </c>
       <c r="X542" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="543" spans="1:24" x14ac:dyDescent="0.3">
@@ -45244,7 +45245,7 @@
         <v>1466</v>
       </c>
       <c r="U543" s="4" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="V543" s="4" t="s">
         <v>2128</v>
@@ -45255,7 +45256,7 @@
       </c>
       <c r="X543" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="544" spans="1:24" x14ac:dyDescent="0.3">
@@ -45304,7 +45305,7 @@
       </c>
       <c r="X544" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="545" spans="1:118" x14ac:dyDescent="0.3">
@@ -45349,7 +45350,7 @@
         <v>1466</v>
       </c>
       <c r="U545" s="4" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="V545" s="4" t="s">
         <v>1909</v>
@@ -45360,7 +45361,7 @@
       </c>
       <c r="X545" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="546" spans="1:118" x14ac:dyDescent="0.3">
@@ -45398,7 +45399,7 @@
         <v>1411</v>
       </c>
       <c r="U546" s="11" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="V546" s="11" t="s">
         <v>3554</v>
@@ -45409,7 +45410,7 @@
       </c>
       <c r="X546" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
       <c r="Y546" s="4"/>
       <c r="Z546" s="4"/>
@@ -45541,7 +45542,7 @@
         <v>1394</v>
       </c>
       <c r="U547" s="11" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="V547" s="11" t="s">
         <v>2274</v>
@@ -45552,7 +45553,7 @@
       </c>
       <c r="X547" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="548" spans="1:118" x14ac:dyDescent="0.3">
@@ -45590,7 +45591,7 @@
         <v>1430</v>
       </c>
       <c r="U548" s="11" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="V548" s="11" t="s">
         <v>3555</v>
@@ -45601,7 +45602,7 @@
       </c>
       <c r="X548" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="Y548" s="4"/>
       <c r="Z548" s="4"/>
@@ -45733,7 +45734,7 @@
         <v>1407</v>
       </c>
       <c r="U549" s="11" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="V549" s="11" t="s">
         <v>2471</v>
@@ -45744,7 +45745,7 @@
       </c>
       <c r="X549" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="550" spans="1:118" x14ac:dyDescent="0.3">
@@ -45782,7 +45783,7 @@
         <v>1467</v>
       </c>
       <c r="U550" s="11" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="V550" s="11" t="s">
         <v>3556</v>
@@ -45793,7 +45794,7 @@
       </c>
       <c r="X550" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="551" spans="1:118" x14ac:dyDescent="0.3">
@@ -45831,7 +45832,7 @@
         <v>1428</v>
       </c>
       <c r="U551" s="11" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="V551" s="11" t="s">
         <v>3557</v>
@@ -45842,7 +45843,7 @@
       </c>
       <c r="X551" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="552" spans="1:118" x14ac:dyDescent="0.3">
@@ -45880,7 +45881,7 @@
         <v>1272</v>
       </c>
       <c r="U552" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V552" s="11" t="s">
         <v>3558</v>
@@ -45891,7 +45892,7 @@
       </c>
       <c r="X552" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="553" spans="1:118" x14ac:dyDescent="0.3">
@@ -45929,7 +45930,7 @@
         <v>1469</v>
       </c>
       <c r="U553" s="11" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="V553" s="11" t="s">
         <v>1701</v>
@@ -45940,7 +45941,7 @@
       </c>
       <c r="X553" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="554" spans="1:118" x14ac:dyDescent="0.3">
@@ -45978,7 +45979,7 @@
         <v>1368</v>
       </c>
       <c r="U554" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V554" s="11" t="s">
         <v>3559</v>
@@ -45989,7 +45990,7 @@
       </c>
       <c r="X554" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="555" spans="1:118" x14ac:dyDescent="0.3">
@@ -46027,7 +46028,7 @@
         <v>1406</v>
       </c>
       <c r="U555" s="11" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="V555" s="11" t="s">
         <v>3560</v>
@@ -46038,7 +46039,7 @@
       </c>
       <c r="X555" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="556" spans="1:118" x14ac:dyDescent="0.3">
@@ -46087,7 +46088,7 @@
       </c>
       <c r="X556" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="557" spans="1:118" x14ac:dyDescent="0.3">
@@ -46125,7 +46126,7 @@
         <v>1305</v>
       </c>
       <c r="U557" s="11" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="V557" s="11" t="s">
         <v>2625</v>
@@ -46136,7 +46137,7 @@
       </c>
       <c r="X557" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="558" spans="1:118" x14ac:dyDescent="0.3">
@@ -46174,7 +46175,7 @@
         <v>1415</v>
       </c>
       <c r="U558" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V558" s="11" t="s">
         <v>3395</v>
@@ -46185,7 +46186,7 @@
       </c>
       <c r="X558" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="559" spans="1:118" x14ac:dyDescent="0.3">
@@ -46223,7 +46224,7 @@
         <v>1419</v>
       </c>
       <c r="U559" s="11" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="V559" s="11" t="s">
         <v>2655</v>
@@ -46234,7 +46235,7 @@
       </c>
       <c r="X559" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="560" spans="1:118" x14ac:dyDescent="0.3">
@@ -46272,7 +46273,7 @@
         <v>1368</v>
       </c>
       <c r="U560" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V560" s="11" t="s">
         <v>2412</v>
@@ -46283,7 +46284,7 @@
       </c>
       <c r="X560" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="561" spans="1:24" x14ac:dyDescent="0.3">
@@ -46321,7 +46322,7 @@
         <v>1422</v>
       </c>
       <c r="U561" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V561" s="11" t="s">
         <v>2435</v>
@@ -46332,7 +46333,7 @@
       </c>
       <c r="X561" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="562" spans="1:24" x14ac:dyDescent="0.3">
@@ -46384,7 +46385,7 @@
       </c>
       <c r="X562" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="563" spans="1:24" x14ac:dyDescent="0.3">
@@ -46422,7 +46423,7 @@
         <v>1368</v>
       </c>
       <c r="U563" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V563" s="11" t="s">
         <v>2177</v>
@@ -46433,7 +46434,7 @@
       </c>
       <c r="X563" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="564" spans="1:24" x14ac:dyDescent="0.3">
@@ -46471,7 +46472,7 @@
         <v>1272</v>
       </c>
       <c r="U564" s="11" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="V564" s="11" t="s">
         <v>2590</v>
@@ -46482,7 +46483,7 @@
       </c>
       <c r="X564" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="565" spans="1:24" x14ac:dyDescent="0.3">
@@ -46520,7 +46521,7 @@
         <v>1474</v>
       </c>
       <c r="U565" s="11" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="V565" s="11" t="s">
         <v>3562</v>
@@ -46531,7 +46532,7 @@
       </c>
       <c r="X565" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="566" spans="1:24" x14ac:dyDescent="0.3">
@@ -46569,7 +46570,7 @@
         <v>1368</v>
       </c>
       <c r="U566" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V566" s="11" t="s">
         <v>2377</v>
@@ -46580,7 +46581,7 @@
       </c>
       <c r="X566" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="567" spans="1:24" x14ac:dyDescent="0.3">
@@ -46632,7 +46633,7 @@
       </c>
       <c r="X567" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="568" spans="1:24" x14ac:dyDescent="0.3">
@@ -46670,7 +46671,7 @@
         <v>1272</v>
       </c>
       <c r="U568" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V568" s="11" t="s">
         <v>2526</v>
@@ -46681,7 +46682,7 @@
       </c>
       <c r="X568" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="569" spans="1:24" x14ac:dyDescent="0.3">
@@ -46719,7 +46720,7 @@
         <v>1272</v>
       </c>
       <c r="U569" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V569" s="11" t="s">
         <v>2444</v>
@@ -46730,7 +46731,7 @@
       </c>
       <c r="X569" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="570" spans="1:24" x14ac:dyDescent="0.3">
@@ -46782,7 +46783,7 @@
       </c>
       <c r="X570" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>149</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="571" spans="1:24" x14ac:dyDescent="0.3">
@@ -46834,7 +46835,7 @@
       </c>
       <c r="X571" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="572" spans="1:24" x14ac:dyDescent="0.3">
@@ -46883,7 +46884,7 @@
       </c>
       <c r="X572" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="573" spans="1:24" x14ac:dyDescent="0.3">
@@ -46921,7 +46922,7 @@
         <v>1388</v>
       </c>
       <c r="U573" s="11" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="V573" s="11" t="s">
         <v>3564</v>
@@ -46932,7 +46933,7 @@
       </c>
       <c r="X573" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="574" spans="1:24" x14ac:dyDescent="0.3">
@@ -46970,7 +46971,7 @@
         <v>1467</v>
       </c>
       <c r="U574" s="11" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="V574" s="11" t="s">
         <v>2208</v>
@@ -46981,7 +46982,7 @@
       </c>
       <c r="X574" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="575" spans="1:24" x14ac:dyDescent="0.3">
@@ -47019,7 +47020,7 @@
         <v>1422</v>
       </c>
       <c r="U575" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V575" s="11" t="s">
         <v>3565</v>
@@ -47030,7 +47031,7 @@
       </c>
       <c r="X575" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="576" spans="1:24" x14ac:dyDescent="0.3">
@@ -47082,7 +47083,7 @@
       </c>
       <c r="X576" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="577" spans="1:118" x14ac:dyDescent="0.3">
@@ -47120,7 +47121,7 @@
         <v>1394</v>
       </c>
       <c r="U577" s="11" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="V577" s="11" t="s">
         <v>3567</v>
@@ -47131,7 +47132,7 @@
       </c>
       <c r="X577" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="578" spans="1:118" x14ac:dyDescent="0.3">
@@ -47180,7 +47181,7 @@
       </c>
       <c r="X578" s="11">
         <f t="shared" ca="1" si="8"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="579" spans="1:118" x14ac:dyDescent="0.3">
@@ -47218,7 +47219,7 @@
         <v>1476</v>
       </c>
       <c r="U579" s="11" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="V579" s="11" t="s">
         <v>1908</v>
@@ -47229,7 +47230,7 @@
       </c>
       <c r="X579" s="11">
         <f t="shared" ref="X579:X625" ca="1" si="9">W579-TODAY()</f>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="580" spans="1:118" x14ac:dyDescent="0.3">
@@ -47267,7 +47268,7 @@
         <v>1272</v>
       </c>
       <c r="U580" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V580" s="11" t="s">
         <v>2303</v>
@@ -47278,7 +47279,7 @@
       </c>
       <c r="X580" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="581" spans="1:118" x14ac:dyDescent="0.3">
@@ -47327,7 +47328,7 @@
       </c>
       <c r="X581" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="582" spans="1:118" x14ac:dyDescent="0.3">
@@ -47365,7 +47366,7 @@
         <v>1336</v>
       </c>
       <c r="U582" s="11" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="V582" s="11" t="s">
         <v>3569</v>
@@ -47376,7 +47377,7 @@
       </c>
       <c r="X582" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="583" spans="1:118" x14ac:dyDescent="0.3">
@@ -47421,7 +47422,7 @@
         <v>1466</v>
       </c>
       <c r="U583" s="4" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="V583" s="4" t="s">
         <v>3570</v>
@@ -47432,7 +47433,7 @@
       </c>
       <c r="X583" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="584" spans="1:118" x14ac:dyDescent="0.3">
@@ -47470,7 +47471,7 @@
         <v>1336</v>
       </c>
       <c r="U584" s="11" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="V584" s="11" t="s">
         <v>2607</v>
@@ -47481,7 +47482,7 @@
       </c>
       <c r="X584" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="585" spans="1:118" x14ac:dyDescent="0.3">
@@ -47519,7 +47520,7 @@
         <v>1388</v>
       </c>
       <c r="U585" s="11" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="V585" s="11" t="s">
         <v>3571</v>
@@ -47530,7 +47531,7 @@
       </c>
       <c r="X585" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="586" spans="1:118" x14ac:dyDescent="0.3">
@@ -47568,7 +47569,7 @@
         <v>1422</v>
       </c>
       <c r="U586" s="11" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="V586" s="11" t="s">
         <v>3572</v>
@@ -47579,7 +47580,7 @@
       </c>
       <c r="X586" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="587" spans="1:118" x14ac:dyDescent="0.3">
@@ -47617,7 +47618,7 @@
         <v>1478</v>
       </c>
       <c r="U587" s="11" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="V587" s="11" t="s">
         <v>1518</v>
@@ -47628,7 +47629,7 @@
       </c>
       <c r="X587" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="588" spans="1:118" x14ac:dyDescent="0.3">
@@ -47669,7 +47670,7 @@
         <v>1296</v>
       </c>
       <c r="U588" s="11" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="V588" s="11" t="s">
         <v>2901</v>
@@ -47680,7 +47681,7 @@
       </c>
       <c r="X588" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
       <c r="Y588" s="4"/>
       <c r="Z588" s="4"/>
@@ -47820,7 +47821,7 @@
       </c>
       <c r="X589" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="590" spans="1:118" x14ac:dyDescent="0.3">
@@ -47858,7 +47859,7 @@
         <v>1415</v>
       </c>
       <c r="U590" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V590" s="11" t="s">
         <v>3573</v>
@@ -47869,7 +47870,7 @@
       </c>
       <c r="X590" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="591" spans="1:118" x14ac:dyDescent="0.3">
@@ -47907,7 +47908,7 @@
         <v>1272</v>
       </c>
       <c r="U591" s="11" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="V591" s="11" t="s">
         <v>2709</v>
@@ -47918,7 +47919,7 @@
       </c>
       <c r="X591" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="592" spans="1:118" x14ac:dyDescent="0.3">
@@ -47956,7 +47957,7 @@
         <v>1434</v>
       </c>
       <c r="U592" s="11" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="V592" s="11" t="s">
         <v>1850</v>
@@ -47967,7 +47968,7 @@
       </c>
       <c r="X592" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="593" spans="1:24" x14ac:dyDescent="0.3">
@@ -48019,7 +48020,7 @@
       </c>
       <c r="X593" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>271</v>
+        <v>120</v>
       </c>
     </row>
     <row r="594" spans="1:24" x14ac:dyDescent="0.3">
@@ -48057,7 +48058,7 @@
         <v>1415</v>
       </c>
       <c r="U594" s="11" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="V594" s="11" t="s">
         <v>3574</v>
@@ -48068,7 +48069,7 @@
       </c>
       <c r="X594" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="595" spans="1:24" x14ac:dyDescent="0.3">
@@ -48106,7 +48107,7 @@
         <v>1434</v>
       </c>
       <c r="U595" s="11" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="V595" s="11" t="s">
         <v>2117</v>
@@ -48117,7 +48118,7 @@
       </c>
       <c r="X595" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="596" spans="1:24" x14ac:dyDescent="0.3">
@@ -48161,7 +48162,7 @@
         <v>1318</v>
       </c>
       <c r="U596" s="11" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="V596" s="11" t="s">
         <v>3053</v>
@@ -48172,7 +48173,7 @@
       </c>
       <c r="X596" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="597" spans="1:24" x14ac:dyDescent="0.3">
@@ -48224,7 +48225,7 @@
       </c>
       <c r="X597" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="598" spans="1:24" x14ac:dyDescent="0.3">
@@ -48262,7 +48263,7 @@
         <v>1424</v>
       </c>
       <c r="U598" s="11" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="V598" s="11" t="s">
         <v>3575</v>
@@ -48273,7 +48274,7 @@
       </c>
       <c r="X598" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="599" spans="1:24" x14ac:dyDescent="0.3">
@@ -48314,7 +48315,7 @@
         <v>716</v>
       </c>
       <c r="V599" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="W599" s="54">
         <f>INDEX([1]ACOMPANHAMENTO!H:H,MATCH(A599,[1]ACOMPANHAMENTO!A:A,0))</f>
@@ -48322,7 +48323,7 @@
       </c>
       <c r="X599" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="600" spans="1:24" x14ac:dyDescent="0.3">
@@ -48371,7 +48372,7 @@
       </c>
       <c r="X600" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="601" spans="1:24" x14ac:dyDescent="0.3">
@@ -48409,7 +48410,7 @@
         <v>1411</v>
       </c>
       <c r="U601" s="11" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="V601" s="11" t="s">
         <v>2523</v>
@@ -48420,7 +48421,7 @@
       </c>
       <c r="X601" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="602" spans="1:24" x14ac:dyDescent="0.3">
@@ -48469,7 +48470,7 @@
       </c>
       <c r="X602" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>241</v>
+        <v>90</v>
       </c>
     </row>
     <row r="603" spans="1:24" x14ac:dyDescent="0.3">
@@ -48518,7 +48519,7 @@
       </c>
       <c r="X603" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-63</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="604" spans="1:24" x14ac:dyDescent="0.3">
@@ -48556,7 +48557,7 @@
         <v>1142</v>
       </c>
       <c r="U604" s="11" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="V604" s="11" t="s">
         <v>3268</v>
@@ -48567,7 +48568,7 @@
       </c>
       <c r="X604" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-216</v>
+        <v>-367</v>
       </c>
     </row>
     <row r="605" spans="1:24" x14ac:dyDescent="0.3">
@@ -48605,7 +48606,7 @@
         <v>1272</v>
       </c>
       <c r="U605" s="11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="V605" s="11" t="s">
         <v>2236</v>
@@ -48616,7 +48617,7 @@
       </c>
       <c r="X605" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="606" spans="1:24" x14ac:dyDescent="0.3">
@@ -48665,7 +48666,7 @@
       </c>
       <c r="X606" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="607" spans="1:24" x14ac:dyDescent="0.3">
@@ -48703,7 +48704,7 @@
         <v>1480</v>
       </c>
       <c r="U607" s="11" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="V607" s="11" t="s">
         <v>3577</v>
@@ -48714,7 +48715,7 @@
       </c>
       <c r="X607" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="608" spans="1:24" x14ac:dyDescent="0.3">
@@ -48752,7 +48753,7 @@
         <v>1480</v>
       </c>
       <c r="U608" s="11" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="V608" s="11" t="s">
         <v>3577</v>
@@ -48763,7 +48764,7 @@
       </c>
       <c r="X608" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="609" spans="1:24" x14ac:dyDescent="0.3">
@@ -48801,7 +48802,7 @@
         <v>1482</v>
       </c>
       <c r="U609" s="11" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="V609" s="11" t="s">
         <v>2263</v>
@@ -48812,7 +48813,7 @@
       </c>
       <c r="X609" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="610" spans="1:24" x14ac:dyDescent="0.3">
@@ -48850,7 +48851,7 @@
         <v>1484</v>
       </c>
       <c r="U610" s="11" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="V610" s="11" t="s">
         <v>1750</v>
@@ -48861,7 +48862,7 @@
       </c>
       <c r="X610" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-32</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="611" spans="1:24" x14ac:dyDescent="0.3">
@@ -48899,7 +48900,7 @@
         <v>1452</v>
       </c>
       <c r="U611" s="11" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="V611" s="11" t="s">
         <v>3578</v>
@@ -48910,7 +48911,7 @@
       </c>
       <c r="X611" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="612" spans="1:24" x14ac:dyDescent="0.3">
@@ -48959,7 +48960,7 @@
       </c>
       <c r="X612" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="613" spans="1:24" x14ac:dyDescent="0.3">
@@ -48997,7 +48998,7 @@
         <v>1424</v>
       </c>
       <c r="U613" s="11" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="V613" s="11" t="s">
         <v>2521</v>
@@ -49008,7 +49009,7 @@
       </c>
       <c r="X613" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-155</v>
+        <v>-306</v>
       </c>
     </row>
     <row r="614" spans="1:24" x14ac:dyDescent="0.3">
@@ -49046,7 +49047,7 @@
         <v>1272</v>
       </c>
       <c r="U614" s="11" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="V614" s="11" t="s">
         <v>2561</v>
@@ -49057,7 +49058,7 @@
       </c>
       <c r="X614" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>90</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="615" spans="1:24" x14ac:dyDescent="0.3">
@@ -49106,7 +49107,7 @@
       </c>
       <c r="X615" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="616" spans="1:24" x14ac:dyDescent="0.3">
@@ -49144,7 +49145,7 @@
         <v>1368</v>
       </c>
       <c r="U616" s="11" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V616" s="11" t="s">
         <v>2307</v>
@@ -49155,7 +49156,7 @@
       </c>
       <c r="X616" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="617" spans="1:24" x14ac:dyDescent="0.3">
@@ -49201,7 +49202,7 @@
       </c>
       <c r="X617" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="618" spans="1:24" x14ac:dyDescent="0.3">
@@ -49250,7 +49251,7 @@
       </c>
       <c r="X618" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="619" spans="1:24" x14ac:dyDescent="0.3">
@@ -49288,7 +49289,7 @@
         <v>1452</v>
       </c>
       <c r="U619" s="11" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="V619" s="11" t="s">
         <v>3367</v>
@@ -49299,7 +49300,7 @@
       </c>
       <c r="X619" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="620" spans="1:24" x14ac:dyDescent="0.3">
@@ -49337,7 +49338,7 @@
         <v>1388</v>
       </c>
       <c r="U620" s="11" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="V620" s="11" t="s">
         <v>2273</v>
@@ -49348,7 +49349,7 @@
       </c>
       <c r="X620" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="621" spans="1:24" x14ac:dyDescent="0.3">
@@ -49397,7 +49398,7 @@
       </c>
       <c r="X621" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>-122</v>
       </c>
     </row>
     <row r="622" spans="1:24" x14ac:dyDescent="0.3">
@@ -49443,7 +49444,7 @@
       </c>
       <c r="X622" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="623" spans="1:24" x14ac:dyDescent="0.3">
@@ -49489,7 +49490,7 @@
       </c>
       <c r="X623" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-581</v>
+        <v>-732</v>
       </c>
     </row>
     <row r="624" spans="1:24" x14ac:dyDescent="0.3">
@@ -49524,7 +49525,7 @@
         <v>1505</v>
       </c>
       <c r="U624" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="V624" t="s">
         <v>3580</v>
@@ -49535,7 +49536,7 @@
       </c>
       <c r="X624" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-124</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="625" spans="1:24" x14ac:dyDescent="0.3">
@@ -49570,7 +49571,7 @@
         <v>1506</v>
       </c>
       <c r="U625" s="11" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="V625" s="11" t="s">
         <v>2226</v>
@@ -49581,7 +49582,7 @@
       </c>
       <c r="X625" s="11">
         <f t="shared" ca="1" si="9"/>
-        <v>-94</v>
+        <v>-245</v>
       </c>
     </row>
     <row r="631" spans="1:24" x14ac:dyDescent="0.3">
@@ -49606,6 +49607,7 @@
       <c r="H633" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="V1:V633" xr:uid="{880570B0-BDCD-4D2B-9E22-E1BFD62BC0C9}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="X2:X625">
     <cfRule type="iconSet" priority="1">
@@ -65866,7 +65868,7 @@
         <v>256</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="D1" s="3"/>
     </row>
@@ -65878,7 +65880,7 @@
         <v>257</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -65926,7 +65928,7 @@
         <v>293</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -65938,7 +65940,7 @@
         <v>294</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -65950,7 +65952,7 @@
         <v>295</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -65962,7 +65964,7 @@
         <v>296</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="D9" s="3"/>
     </row>
@@ -65974,7 +65976,7 @@
         <v>297</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="D10" s="3"/>
     </row>
@@ -65986,7 +65988,7 @@
         <v>298</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="D11" s="3"/>
     </row>
@@ -65998,7 +66000,7 @@
         <v>299</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -66082,7 +66084,7 @@
         <v>305</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="D19" s="3"/>
     </row>
@@ -66094,7 +66096,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="D20" s="3"/>
     </row>
@@ -66190,7 +66192,7 @@
         <v>34</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="D28" s="3"/>
     </row>
@@ -66310,7 +66312,7 @@
         <v>320</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="D38" s="3"/>
     </row>
@@ -66322,7 +66324,7 @@
         <v>321</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="D39" s="3"/>
     </row>
@@ -66334,7 +66336,7 @@
         <v>322</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="D40" s="3"/>
     </row>
@@ -66346,7 +66348,7 @@
         <v>323</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="D41" s="3"/>
     </row>
@@ -66370,7 +66372,7 @@
         <v>325</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="D43" s="3"/>
     </row>
@@ -66454,7 +66456,7 @@
         <v>57</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="D50" s="3"/>
     </row>
@@ -66466,7 +66468,7 @@
         <v>59</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="D51" s="3"/>
     </row>
@@ -66478,7 +66480,7 @@
         <v>330</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="D52" s="3"/>
     </row>
@@ -66526,7 +66528,7 @@
         <v>66</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="D56" s="3"/>
     </row>
@@ -66646,7 +66648,7 @@
         <v>78</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="D66" s="3"/>
     </row>
@@ -66670,7 +66672,7 @@
         <v>81</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="D68" s="3"/>
     </row>
@@ -66730,7 +66732,7 @@
         <v>346</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="D73" s="3"/>
     </row>
@@ -66838,7 +66840,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="D82" s="3"/>
     </row>
@@ -66934,7 +66936,7 @@
         <v>108</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="D90" s="3"/>
     </row>
@@ -66958,7 +66960,7 @@
         <v>450</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="D92" s="3"/>
     </row>
@@ -67030,7 +67032,7 @@
         <v>122</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="D98" s="3"/>
     </row>
@@ -67138,7 +67140,7 @@
         <v>444</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D107" s="3"/>
     </row>
@@ -67150,7 +67152,7 @@
         <v>366</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D108" s="3"/>
     </row>
@@ -67186,7 +67188,7 @@
         <v>369</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="D111" s="3"/>
     </row>
@@ -67198,7 +67200,7 @@
         <v>140</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="D112" s="3"/>
     </row>
@@ -67210,7 +67212,7 @@
         <v>142</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="D113" s="3"/>
     </row>
@@ -67246,7 +67248,7 @@
         <v>372</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="D116" s="3"/>
     </row>
@@ -67258,7 +67260,7 @@
         <v>373</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="D117" s="3"/>
     </row>
@@ -67270,7 +67272,7 @@
         <v>374</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="D118" s="3"/>
     </row>
@@ -67306,7 +67308,7 @@
         <v>376</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="D121" s="3"/>
     </row>
@@ -67318,7 +67320,7 @@
         <v>377</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="D122" s="3"/>
     </row>
@@ -67330,7 +67332,7 @@
         <v>379</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="D123" s="3"/>
     </row>
@@ -67582,7 +67584,7 @@
         <v>260</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="D144" s="3"/>
     </row>
@@ -67594,7 +67596,7 @@
         <v>392</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="D145" s="3"/>
     </row>
@@ -67606,7 +67608,7 @@
         <v>261</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="D146" s="3"/>
     </row>
@@ -67618,7 +67620,7 @@
         <v>262</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="D147" s="3"/>
     </row>
@@ -67642,7 +67644,7 @@
         <v>393</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="D149" s="3"/>
     </row>
@@ -67654,7 +67656,7 @@
         <v>394</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="D150" s="3"/>
     </row>
@@ -67666,7 +67668,7 @@
         <v>264</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="D151" s="3"/>
     </row>
@@ -67678,7 +67680,7 @@
         <v>1040</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="D152" s="3"/>
     </row>
@@ -67714,7 +67716,7 @@
         <v>265</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="D155" s="3"/>
     </row>
@@ -67738,7 +67740,7 @@
         <v>533</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="D157" s="3"/>
     </row>
@@ -67750,7 +67752,7 @@
         <v>398</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="D158" s="3"/>
     </row>
@@ -67774,7 +67776,7 @@
         <v>267</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="D160" s="3"/>
     </row>
@@ -67786,7 +67788,7 @@
         <v>268</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="D161" s="3"/>
     </row>
@@ -67798,7 +67800,7 @@
         <v>399</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="D162" s="3"/>
     </row>
@@ -67810,7 +67812,7 @@
         <v>269</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="D163" s="3"/>
     </row>
@@ -67822,7 +67824,7 @@
         <v>400</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="D164" s="3"/>
     </row>
@@ -67834,7 +67836,7 @@
         <v>401</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="D165" s="3"/>
     </row>
@@ -67846,7 +67848,7 @@
         <v>402</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="D166" s="3"/>
     </row>
@@ -67858,7 +67860,7 @@
         <v>403</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="D167" s="3"/>
     </row>
@@ -67870,7 +67872,7 @@
         <v>404</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="D168" s="3"/>
     </row>
@@ -67882,7 +67884,7 @@
         <v>405</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="D169" s="3"/>
     </row>
@@ -67894,7 +67896,7 @@
         <v>270</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="D170" s="3"/>
     </row>
@@ -67906,7 +67908,7 @@
         <v>406</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="D171" s="3"/>
     </row>
@@ -67918,7 +67920,7 @@
         <v>407</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D172" s="3"/>
     </row>
@@ -67930,7 +67932,7 @@
         <v>408</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D173" s="3"/>
     </row>
@@ -67942,7 +67944,7 @@
         <v>409</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="D174" s="3"/>
     </row>
@@ -67954,7 +67956,7 @@
         <v>410</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="D175" s="3"/>
     </row>
@@ -67966,7 +67968,7 @@
         <v>411</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="D176" s="3"/>
     </row>
@@ -67978,7 +67980,7 @@
         <v>271</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="D177" s="3"/>
     </row>
@@ -67990,7 +67992,7 @@
         <v>412</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="D178" s="3"/>
     </row>
@@ -68002,7 +68004,7 @@
         <v>413</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="D179" s="3"/>
     </row>
@@ -68038,7 +68040,7 @@
         <v>272</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="D182" s="3"/>
     </row>
@@ -68050,7 +68052,7 @@
         <v>273</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="D183" s="3"/>
     </row>
@@ -68062,7 +68064,7 @@
         <v>415</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="D184" s="3"/>
     </row>
@@ -68074,7 +68076,7 @@
         <v>416</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="D185" s="3"/>
     </row>
@@ -68086,7 +68088,7 @@
         <v>274</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="D186" s="3"/>
     </row>
@@ -68098,7 +68100,7 @@
         <v>417</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="D187" s="3"/>
     </row>
@@ -68110,7 +68112,7 @@
         <v>418</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="D188" s="3"/>
     </row>
@@ -68122,7 +68124,7 @@
         <v>419</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="D189" s="3"/>
     </row>
@@ -68134,7 +68136,7 @@
         <v>275</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="D190" s="3"/>
     </row>
@@ -68146,7 +68148,7 @@
         <v>276</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="D191" s="3"/>
     </row>
@@ -68158,7 +68160,7 @@
         <v>420</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="D192" s="3"/>
     </row>
@@ -68194,7 +68196,7 @@
         <v>421</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="D195" s="3"/>
     </row>
@@ -68206,7 +68208,7 @@
         <v>279</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="D196" s="3"/>
     </row>
@@ -68218,7 +68220,7 @@
         <v>280</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="D197" s="3"/>
     </row>
@@ -68230,7 +68232,7 @@
         <v>281</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="D198" s="3"/>
     </row>
@@ -68242,7 +68244,7 @@
         <v>282</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="D199" s="3"/>
     </row>
@@ -68254,7 +68256,7 @@
         <v>283</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="D200" s="3"/>
     </row>
@@ -68266,7 +68268,7 @@
         <v>284</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="D201" s="3"/>
     </row>
@@ -68278,7 +68280,7 @@
         <v>285</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="D202" s="3"/>
     </row>
@@ -68290,7 +68292,7 @@
         <v>422</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="D203" s="3"/>
     </row>
@@ -68314,7 +68316,7 @@
         <v>424</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="D205" s="3"/>
     </row>
@@ -68326,7 +68328,7 @@
         <v>425</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="D206" s="3"/>
     </row>
@@ -68338,7 +68340,7 @@
         <v>426</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="D207" s="3"/>
     </row>
@@ -68362,7 +68364,7 @@
         <v>287</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D209" s="3"/>
     </row>
@@ -68374,7 +68376,7 @@
         <v>288</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D210" s="3"/>
     </row>
@@ -68386,7 +68388,7 @@
         <v>289</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D211" s="3"/>
     </row>
@@ -68398,7 +68400,7 @@
         <v>290</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D212" s="3"/>
     </row>
@@ -68410,7 +68412,7 @@
         <v>291</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="D213" s="3"/>
     </row>
@@ -68434,7 +68436,7 @@
         <v>462</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="D215" s="3"/>
     </row>
@@ -68458,7 +68460,7 @@
         <v>466</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="D217" s="3"/>
     </row>
@@ -68482,7 +68484,7 @@
         <v>155</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="D219" s="3"/>
     </row>
@@ -68494,7 +68496,7 @@
         <v>467</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="D220" s="3"/>
     </row>
@@ -68518,7 +68520,7 @@
         <v>480</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="D222" s="3"/>
     </row>
@@ -68530,7 +68532,7 @@
         <v>482</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="D223" s="3"/>
     </row>
@@ -68542,7 +68544,7 @@
         <v>486</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="D224" s="3"/>
     </row>
@@ -68554,7 +68556,7 @@
         <v>485</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="D225" s="3"/>
     </row>
@@ -68566,7 +68568,7 @@
         <v>488</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="D226" s="3"/>
     </row>
@@ -68578,7 +68580,7 @@
         <v>490</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="D227" s="3"/>
     </row>
@@ -68590,7 +68592,7 @@
         <v>494</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="D228" s="3"/>
     </row>
@@ -68602,7 +68604,7 @@
         <v>495</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="D229" s="3"/>
     </row>
@@ -68614,7 +68616,7 @@
         <v>496</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="D230" s="3"/>
     </row>
@@ -68626,7 +68628,7 @@
         <v>502</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="D231" s="3"/>
     </row>
@@ -68638,7 +68640,7 @@
         <v>503</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="D232" s="3"/>
     </row>
@@ -68650,7 +68652,7 @@
         <v>505</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="D233" s="3"/>
     </row>
@@ -68662,7 +68664,7 @@
         <v>506</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="D234" s="3"/>
     </row>
@@ -68674,7 +68676,7 @@
         <v>508</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="D235" s="3"/>
     </row>
@@ -68686,7 +68688,7 @@
         <v>509</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="D236" s="3"/>
     </row>
@@ -68698,7 +68700,7 @@
         <v>511</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="D237" s="3"/>
     </row>
@@ -68722,7 +68724,7 @@
         <v>518</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="D239" s="3"/>
     </row>
@@ -68734,7 +68736,7 @@
         <v>519</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="D240" s="3"/>
     </row>
@@ -68746,7 +68748,7 @@
         <v>409</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="D241" s="3"/>
     </row>
@@ -68758,7 +68760,7 @@
         <v>522</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="D242" s="3"/>
     </row>
@@ -68770,7 +68772,7 @@
         <v>523</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="D243" s="3"/>
     </row>
@@ -68782,7 +68784,7 @@
         <v>526</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="D244" s="3"/>
     </row>
@@ -68794,7 +68796,7 @@
         <v>528</v>
       </c>
       <c r="C245" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="D245" s="3"/>
     </row>
@@ -68806,7 +68808,7 @@
         <v>283</v>
       </c>
       <c r="C246" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="D246" s="3"/>
     </row>
